--- a/AAII_Financials/Quarterly/MCRAA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCRAA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>MCRAA</t>
   </si>
@@ -656,227 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45045</v>
+      </c>
+      <c r="E7" s="2">
         <v>44954</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44863</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44772</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44681</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44591</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44499</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44408</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44317</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44226</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44135</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44044</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43953</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43832</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43771</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43680</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43582</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43491</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43400</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43309</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43218</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43127</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43036</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42945</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42854</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42763</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42672</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42581</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E8" s="3">
         <v>30800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>31400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>27600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>24100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>28100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>29900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>23100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -884,177 +890,183 @@
         <v>22800</v>
       </c>
       <c r="E9" s="3">
+        <v>22800</v>
+      </c>
+      <c r="F9" s="3">
         <v>23500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>23400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>23100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15300</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>17000</v>
       </c>
       <c r="R9" s="3">
         <v>17000</v>
       </c>
       <c r="S9" s="3">
+        <v>17000</v>
+      </c>
+      <c r="T9" s="3">
         <v>14400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>17200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>18300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>20700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>22500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E10" s="3">
         <v>8000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5800</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>7400</v>
       </c>
       <c r="AC10" s="3">
         <v>7400</v>
       </c>
       <c r="AD10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AE10" s="3">
         <v>5300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,8 +1098,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1188,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,8 +1280,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1353,8 +1372,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1442,8 +1464,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1497,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E17" s="3">
         <v>28900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>20400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>25500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>27500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>22500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>24100</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E18" s="3">
         <v>1900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>400</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>1100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,49 +1715,50 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
       </c>
       <c r="K20" s="3">
+        <v>200</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>200</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
@@ -1740,7 +1773,7 @@
         <v>200</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
@@ -1770,10 +1803,13 @@
         <v>100</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1861,8 +1897,11 @@
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1887,8 +1926,8 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
@@ -1896,11 +1935,11 @@
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
@@ -1908,11 +1947,11 @@
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
@@ -1920,11 +1959,11 @@
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
@@ -1932,11 +1971,11 @@
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
@@ -1944,192 +1983,201 @@
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E23" s="3">
         <v>2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
       </c>
       <c r="U24" s="3">
+        <v>100</v>
+      </c>
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>800</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>1000</v>
       </c>
       <c r="AC24" s="3">
         <v>1000</v>
       </c>
       <c r="AD24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2265,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1700</v>
-      </c>
-      <c r="E26" s="3">
-        <v>2900</v>
       </c>
       <c r="F26" s="3">
         <v>2900</v>
       </c>
       <c r="G26" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="H26" s="3">
         <v>2500</v>
       </c>
       <c r="I26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J26" s="3">
         <v>2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1700</v>
-      </c>
-      <c r="E27" s="3">
-        <v>2900</v>
       </c>
       <c r="F27" s="3">
         <v>2900</v>
       </c>
       <c r="G27" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="H27" s="3">
         <v>2500</v>
       </c>
       <c r="I27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J27" s="3">
         <v>2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2541,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2522,8 +2582,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -2531,11 +2591,11 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2543,14 +2603,14 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>400</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2573,8 +2633,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2725,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,49 +2817,52 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>-200</v>
       </c>
       <c r="K32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-200</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
@@ -2808,7 +2877,7 @@
         <v>-200</v>
       </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
@@ -2838,99 +2907,105 @@
         <v>-100</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1700</v>
-      </c>
-      <c r="E33" s="3">
-        <v>2900</v>
       </c>
       <c r="F33" s="3">
         <v>2900</v>
       </c>
       <c r="G33" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="H33" s="3">
         <v>2500</v>
       </c>
       <c r="I33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J33" s="3">
         <v>2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>900</v>
-      </c>
-      <c r="V33" s="3">
-        <v>100</v>
       </c>
       <c r="W33" s="3">
         <v>100</v>
       </c>
       <c r="X33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y33" s="3">
         <v>700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3093,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1700</v>
-      </c>
-      <c r="E35" s="3">
-        <v>2900</v>
       </c>
       <c r="F35" s="3">
         <v>2900</v>
       </c>
       <c r="G35" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="H35" s="3">
         <v>2500</v>
       </c>
       <c r="I35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J35" s="3">
         <v>2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>900</v>
-      </c>
-      <c r="V35" s="3">
-        <v>100</v>
       </c>
       <c r="W35" s="3">
         <v>100</v>
       </c>
       <c r="X35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y35" s="3">
         <v>700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45045</v>
+      </c>
+      <c r="E38" s="2">
         <v>44954</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44863</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44772</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44681</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44591</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44499</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44408</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44317</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44226</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44135</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44044</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43953</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43832</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43771</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43680</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43582</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43491</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43400</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43309</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43218</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43127</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43036</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42945</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42854</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42763</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42672</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42581</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3318,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,162 +3352,166 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E41" s="3">
         <v>15400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>20400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>27600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>33900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>32300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>29200</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>28100</v>
       </c>
       <c r="AA41" s="3">
         <v>28100</v>
       </c>
       <c r="AB41" s="3">
+        <v>28100</v>
+      </c>
+      <c r="AC41" s="3">
         <v>23400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E42" s="3">
         <v>10700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8700</v>
-      </c>
-      <c r="H42" s="3">
-        <v>6500</v>
       </c>
       <c r="I42" s="3">
         <v>6500</v>
       </c>
       <c r="J42" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K42" s="3">
         <v>8600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>7200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>10900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>13200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>12100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>9500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>7800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2200</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
       <c r="X42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="3">
         <v>500</v>
@@ -3431,13 +3520,13 @@
         <v>500</v>
       </c>
       <c r="AA42" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AB42" s="3">
         <v>400</v>
       </c>
       <c r="AC42" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AD42" s="3">
         <v>500</v>
@@ -3445,364 +3534,379 @@
       <c r="AE42" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E43" s="3">
         <v>19900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>14500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>15400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>13600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E44" s="3">
         <v>29700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>31500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>18400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>15600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>18100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>19500</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>19800</v>
       </c>
       <c r="R44" s="3">
         <v>19800</v>
       </c>
       <c r="S44" s="3">
+        <v>19800</v>
+      </c>
+      <c r="T44" s="3">
         <v>16100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>15500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>17900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>18400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>14000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>13300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>17400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>19600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>24900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>55900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>300</v>
       </c>
       <c r="K45" s="3">
         <v>300</v>
       </c>
       <c r="L45" s="3">
+        <v>300</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
-      </c>
-      <c r="S45" s="3">
-        <v>400</v>
       </c>
       <c r="T45" s="3">
         <v>400</v>
       </c>
       <c r="U45" s="3">
+        <v>400</v>
+      </c>
+      <c r="V45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>77700</v>
+      </c>
+      <c r="E46" s="3">
         <v>76100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>79500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>76800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>71200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>68700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>67000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>63100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>62900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>62100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>62700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>63000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>57500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>59200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>59300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>59800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>59300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>59100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>59800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>60200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>59400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>59200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>61500</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>60000</v>
       </c>
       <c r="AA46" s="3">
         <v>60000</v>
       </c>
       <c r="AB46" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AC46" s="3">
         <v>58300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>58000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>58200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3819,16 +3923,16 @@
         <v>4000</v>
       </c>
       <c r="H47" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="I47" s="3">
         <v>4100</v>
       </c>
       <c r="J47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K47" s="3">
         <v>4300</v>
-      </c>
-      <c r="K47" s="3">
-        <v>3200</v>
       </c>
       <c r="L47" s="3">
         <v>3200</v>
@@ -3837,46 +3941,46 @@
         <v>3200</v>
       </c>
       <c r="N47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O47" s="3">
         <v>3800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7900</v>
-      </c>
-      <c r="R47" s="3">
-        <v>7800</v>
       </c>
       <c r="S47" s="3">
         <v>7800</v>
       </c>
       <c r="T47" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="U47" s="3">
         <v>7600</v>
       </c>
       <c r="V47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="W47" s="3">
         <v>7700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>7200</v>
       </c>
       <c r="AB47" s="3">
         <v>7200</v>
@@ -3885,102 +3989,108 @@
         <v>7200</v>
       </c>
       <c r="AD47" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="AE47" s="3">
         <v>7100</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>5100</v>
       </c>
       <c r="H48" s="3">
         <v>5100</v>
       </c>
       <c r="I48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J48" s="3">
         <v>5200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4068,8 +4178,11 @@
       <c r="AE49" s="3">
         <v>2800</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4270,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,8 +4362,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4303,13 +4422,13 @@
         <v>2300</v>
       </c>
       <c r="U52" s="3">
-        <v>3400</v>
+        <v>2300</v>
       </c>
       <c r="V52" s="3">
         <v>3400</v>
       </c>
       <c r="W52" s="3">
-        <v>2300</v>
+        <v>3400</v>
       </c>
       <c r="X52" s="3">
         <v>2300</v>
@@ -4335,8 +4454,11 @@
       <c r="AE52" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4546,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E54" s="3">
         <v>90500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>93900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>91000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>85400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>83000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>81400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>77900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>76700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>76200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>76900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>77900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>76600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>78600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>78700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>79400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>78900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>78700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>80800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>80400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>79300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>79400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>81600</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>80000</v>
       </c>
       <c r="AA54" s="3">
         <v>80000</v>
       </c>
       <c r="AB54" s="3">
+        <v>80000</v>
+      </c>
+      <c r="AC54" s="3">
         <v>78400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>78300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>78600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4674,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,97 +4708,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2200</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>2500</v>
       </c>
       <c r="Z57" s="3">
         <v>2500</v>
       </c>
       <c r="AA57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AB57" s="3">
         <v>3300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4757,186 +4890,195 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E59" s="3">
         <v>3400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1800</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1500</v>
       </c>
       <c r="O59" s="3">
         <v>1500</v>
       </c>
       <c r="P59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2000</v>
-      </c>
-      <c r="V59" s="3">
-        <v>1800</v>
       </c>
       <c r="W59" s="3">
         <v>1800</v>
       </c>
       <c r="X59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Y59" s="3">
         <v>1600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E60" s="3">
         <v>6400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5024,8 +5166,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5039,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>500</v>
@@ -5051,7 +5196,7 @@
         <v>500</v>
       </c>
       <c r="K62" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="L62" s="3">
         <v>700</v>
@@ -5075,46 +5220,49 @@
         <v>700</v>
       </c>
       <c r="S62" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="T62" s="3">
         <v>600</v>
       </c>
       <c r="U62" s="3">
+        <v>600</v>
+      </c>
+      <c r="V62" s="3">
         <v>1700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA62" s="3">
         <v>2300</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE62" s="3">
         <v>2300</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5350,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5442,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5534,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E66" s="3">
         <v>6500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>4600</v>
       </c>
       <c r="L66" s="3">
         <v>4600</v>
       </c>
       <c r="M66" s="3">
+        <v>4600</v>
+      </c>
+      <c r="N66" s="3">
         <v>5400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5662,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5752,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5844,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +5936,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6028,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>83600</v>
+      </c>
+      <c r="E72" s="3">
         <v>81800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>81500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>79000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>76400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>74200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>71900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>70000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>69900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>69300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>69200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>69500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>71100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>71900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>71700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>71000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>71800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>71700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>72000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>72600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>72800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>73200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>72800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>71800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>71400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>71000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>69700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>68500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>68200</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6212,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6304,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6396,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E76" s="3">
         <v>84100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>83800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>81200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>78700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>76400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>74200</v>
-      </c>
-      <c r="J76" s="3">
-        <v>72200</v>
       </c>
       <c r="K76" s="3">
         <v>72200</v>
       </c>
       <c r="L76" s="3">
+        <v>72200</v>
+      </c>
+      <c r="M76" s="3">
         <v>71600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>71500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>73200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>74300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>74000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>73300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>74100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>74000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>74200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>75000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>75200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>75600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>75200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>74200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>73800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>73400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>72100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>70900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6580,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45045</v>
+      </c>
+      <c r="E80" s="2">
         <v>44954</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44863</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44772</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44681</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44591</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44499</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44408</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44317</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44226</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44135</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44044</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43953</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43832</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43771</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43680</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43582</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43491</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43400</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43309</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43218</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43127</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43036</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42945</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42854</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42763</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42672</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42581</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1700</v>
-      </c>
-      <c r="E81" s="3">
-        <v>2900</v>
       </c>
       <c r="F81" s="3">
         <v>2900</v>
       </c>
       <c r="G81" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="H81" s="3">
         <v>2500</v>
       </c>
       <c r="I81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J81" s="3">
         <v>2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>900</v>
-      </c>
-      <c r="V81" s="3">
-        <v>100</v>
       </c>
       <c r="W81" s="3">
         <v>100</v>
       </c>
       <c r="X81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y81" s="3">
         <v>700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,8 +6805,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6697,8 +6895,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6987,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7079,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7171,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7263,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7355,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,25 +7483,26 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-300</v>
       </c>
       <c r="G91" s="3">
         <v>-300</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -7291,16 +7511,16 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -7330,31 +7550,34 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7665,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7757,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2800</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>2200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-400</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,16 +7885,17 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-300</v>
       </c>
       <c r="F96" s="3">
         <v>-300</v>
@@ -7710,10 +7943,10 @@
         <v>-300</v>
       </c>
       <c r="U96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1500</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-300</v>
       </c>
       <c r="W96" s="3">
         <v>-300</v>
@@ -7742,8 +7975,11 @@
       <c r="AE96" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8067,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8159,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,16 +8251,19 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-300</v>
       </c>
       <c r="F100" s="3">
         <v>-300</v>
@@ -8033,49 +8278,49 @@
         <v>-300</v>
       </c>
       <c r="J100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-800</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-600</v>
       </c>
       <c r="L100" s="3">
         <v>-600</v>
       </c>
       <c r="M100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N100" s="3">
         <v>-800</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-400</v>
       </c>
       <c r="O100" s="3">
         <v>-400</v>
       </c>
       <c r="P100" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="Q100" s="3">
         <v>-300</v>
       </c>
       <c r="R100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S100" s="3">
         <v>-1600</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-300</v>
       </c>
       <c r="T100" s="3">
         <v>-300</v>
       </c>
       <c r="U100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V100" s="3">
         <v>-1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-400</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-300</v>
       </c>
       <c r="Y100" s="3">
         <v>-300</v>
@@ -8084,10 +8329,10 @@
         <v>-300</v>
       </c>
       <c r="AA100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-900</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>-300</v>
       </c>
       <c r="AC100" s="3">
         <v>-300</v>
@@ -8096,10 +8341,13 @@
         <v>-300</v>
       </c>
       <c r="AE100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8187,93 +8435,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1100</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>4700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCRAA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCRAA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>MCRAA</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -668,405 +668,456 @@
     <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45409</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45318</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45227</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45136</v>
+      </c>
+      <c r="H7" s="2">
         <v>45045</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>44954</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>44863</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>44772</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>44591</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>44499</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>44317</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>44226</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44044</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>43953</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="U7" s="2">
         <v>43832</v>
       </c>
-      <c r="R7" s="2">
+      <c r="V7" s="2">
         <v>43771</v>
       </c>
-      <c r="S7" s="2">
+      <c r="W7" s="2">
         <v>43680</v>
       </c>
-      <c r="T7" s="2">
+      <c r="X7" s="2">
         <v>43582</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>43491</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <v>43400</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <v>43309</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AB7" s="2">
         <v>43218</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AC7" s="2">
         <v>43127</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AD7" s="2">
         <v>43036</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AE7" s="2">
         <v>42945</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AF7" s="2">
         <v>42854</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AG7" s="2">
         <v>42763</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AH7" s="2">
         <v>42672</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AI7" s="2">
         <v>42581</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AJ7" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>25800</v>
+      </c>
+      <c r="F8" s="3">
+        <v>32800</v>
+      </c>
+      <c r="G8" s="3">
+        <v>28600</v>
+      </c>
+      <c r="H8" s="3">
         <v>31500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="I8" s="3">
         <v>30800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="J8" s="3">
         <v>33800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="K8" s="3">
         <v>33000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="L8" s="3">
         <v>32800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="M8" s="3">
         <v>31400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="N8" s="3">
         <v>27600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="O8" s="3">
         <v>21400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="P8" s="3">
         <v>21600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="Q8" s="3">
         <v>20200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="R8" s="3">
         <v>18900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="S8" s="3">
         <v>12000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="T8" s="3">
         <v>14300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>20300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>22700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>22200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>18600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>20700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>20600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AA8" s="3">
         <v>14900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AB8" s="3">
         <v>16200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AC8" s="3">
         <v>20500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AD8" s="3">
         <v>22400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AE8" s="3">
         <v>22200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AF8" s="3">
         <v>24100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AG8" s="3">
         <v>28100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AH8" s="3">
         <v>29900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AI8" s="3">
         <v>23100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AJ8" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>18800</v>
+      </c>
+      <c r="F9" s="3">
+        <v>22900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>21800</v>
+      </c>
+      <c r="H9" s="3">
         <v>22800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="I9" s="3">
         <v>22800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="J9" s="3">
         <v>23500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="K9" s="3">
         <v>23400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="L9" s="3">
         <v>23100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="M9" s="3">
         <v>22300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="N9" s="3">
         <v>19600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="O9" s="3">
         <v>16000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="P9" s="3">
         <v>15600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="Q9" s="3">
         <v>14700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="R9" s="3">
         <v>13900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="S9" s="3">
         <v>9900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="T9" s="3">
         <v>11600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="U9" s="3">
         <v>15300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="V9" s="3">
         <v>17000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="W9" s="3">
         <v>17000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="X9" s="3">
         <v>14400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>16200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>15300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>11300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AB9" s="3">
         <v>12200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AC9" s="3">
         <v>15500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AD9" s="3">
         <v>16200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AE9" s="3">
         <v>17200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AF9" s="3">
         <v>18300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AG9" s="3">
         <v>20700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AH9" s="3">
         <v>22500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AI9" s="3">
         <v>17800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AJ9" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>9900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H10" s="3">
         <v>8700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="I10" s="3">
         <v>8000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="J10" s="3">
         <v>10300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="K10" s="3">
         <v>9600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="L10" s="3">
         <v>9700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="M10" s="3">
         <v>9100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="N10" s="3">
         <v>8000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="O10" s="3">
         <v>5400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="P10" s="3">
         <v>6000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>5500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>5000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>2100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>2700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>5000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>5700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>5200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>4200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>4500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>5300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
         <v>3600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AB10" s="3">
         <v>4000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AC10" s="3">
         <v>5000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AD10" s="3">
         <v>6200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AE10" s="3">
         <v>5000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AF10" s="3">
         <v>5800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AG10" s="3">
         <v>7400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AH10" s="3">
         <v>7400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AI10" s="3">
         <v>5300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AJ10" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,8 +1150,12 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,8 +1246,20 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,8 +1350,20 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1375,8 +1454,20 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1467,8 +1558,20 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1601,220 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>24400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>28900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>27300</v>
+      </c>
+      <c r="H17" s="3">
         <v>28700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="I17" s="3">
         <v>28900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="J17" s="3">
         <v>29500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="K17" s="3">
         <v>29600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="L17" s="3">
         <v>29000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="M17" s="3">
         <v>28000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="N17" s="3">
         <v>24700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="O17" s="3">
         <v>20600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>20100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>19400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="R17" s="3">
         <v>18300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>13600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>15000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>19700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>21500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>21400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>18200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>20700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>19500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>15200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AB17" s="3">
         <v>16100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <v>19900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AD17" s="3">
         <v>20400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AE17" s="3">
         <v>21200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AF17" s="3">
         <v>22300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AG17" s="3">
         <v>25500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <v>27500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AI17" s="3">
         <v>22500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AJ17" s="3">
         <v>24100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H18" s="3">
         <v>2800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="I18" s="3">
         <v>1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="J18" s="3">
         <v>4300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="K18" s="3">
         <v>3400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="L18" s="3">
         <v>3800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="M18" s="3">
         <v>3400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="N18" s="3">
         <v>2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="O18" s="3">
         <v>800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="P18" s="3">
         <v>1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="Q18" s="3">
         <v>800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="R18" s="3">
         <v>600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>-1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="T18" s="3">
         <v>-700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>1200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>1100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <v>-300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AB18" s="3">
         <v>100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AC18" s="3">
         <v>600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AD18" s="3">
         <v>2000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AE18" s="3">
         <v>1000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AF18" s="3">
         <v>1800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AG18" s="3">
         <v>2600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AH18" s="3">
         <v>2400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AI18" s="3">
         <v>600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AJ18" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,76 +1847,80 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>900</v>
+      </c>
+      <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>400</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>200</v>
       </c>
       <c r="V20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
@@ -1806,10 +1941,22 @@
         <v>100</v>
       </c>
       <c r="AF20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1900,8 +2047,20 @@
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1929,14 +2088,14 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1992,192 +2151,228 @@
       <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="E23" s="3">
         <v>2300</v>
       </c>
       <c r="F23" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J23" s="3">
         <v>4100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="K23" s="3">
         <v>3400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="L23" s="3">
         <v>3500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="M23" s="3">
         <v>3400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="N23" s="3">
         <v>3100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="O23" s="3">
         <v>1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="P23" s="3">
         <v>1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="Q23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="S23" s="3">
         <v>-1500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="T23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <v>900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <v>1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <v>1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <v>500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Y23" s="3">
         <v>200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>1200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AC23" s="3">
         <v>700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AD23" s="3">
         <v>2100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AE23" s="3">
         <v>1100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AF23" s="3">
         <v>2000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AG23" s="3">
         <v>2600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AH23" s="3">
         <v>2500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AI23" s="3">
         <v>700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AJ23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E24" s="3">
         <v>600</v>
       </c>
       <c r="F24" s="3">
+        <v>700</v>
+      </c>
+      <c r="G24" s="3">
+        <v>400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>900</v>
+      </c>
+      <c r="I24" s="3">
+        <v>600</v>
+      </c>
+      <c r="J24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="P24" s="3">
         <v>500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-100</v>
       </c>
       <c r="Q24" s="3">
         <v>300</v>
       </c>
       <c r="R24" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="S24" s="3">
-        <v>200</v>
+        <v>-400</v>
       </c>
       <c r="T24" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="U24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="V24" s="3">
         <v>400</v>
       </c>
       <c r="W24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AE24" s="3">
         <v>400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AF24" s="3">
         <v>800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AG24" s="3">
         <v>1000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AH24" s="3">
         <v>1000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AI24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AJ24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,8 +2463,20 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2277,91 +2484,103 @@
         <v>2100</v>
       </c>
       <c r="E26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F26" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I26" s="3">
         <v>1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="J26" s="3">
         <v>2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="K26" s="3">
         <v>2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="L26" s="3">
         <v>2500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="M26" s="3">
         <v>2500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="N26" s="3">
         <v>2200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="O26" s="3">
         <v>900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="P26" s="3">
         <v>1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="R26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="S26" s="3">
         <v>-1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="T26" s="3">
         <v>-500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="U26" s="3">
         <v>600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="V26" s="3">
         <v>1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="W26" s="3">
         <v>800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="X26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="Y26" s="3">
         <v>100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z26" s="3">
         <v>900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AB26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AC26" s="3">
         <v>700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AD26" s="3">
         <v>1300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AE26" s="3">
         <v>700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AF26" s="3">
         <v>1200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AG26" s="3">
         <v>1600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AH26" s="3">
         <v>1500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AI26" s="3">
         <v>600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AJ26" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2369,91 +2588,103 @@
         <v>2100</v>
       </c>
       <c r="E27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H27" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I27" s="3">
         <v>1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="J27" s="3">
         <v>2900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="K27" s="3">
         <v>2900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="L27" s="3">
         <v>2500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="M27" s="3">
         <v>2500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="N27" s="3">
         <v>2200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="O27" s="3">
         <v>900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="P27" s="3">
         <v>1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AB27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AC27" s="3">
         <v>700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AD27" s="3">
         <v>1300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AE27" s="3">
         <v>700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AF27" s="3">
         <v>1200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AG27" s="3">
         <v>1600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AH27" s="3">
         <v>1500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AI27" s="3">
         <v>600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AJ27" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2775,20 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2585,14 +2828,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2607,22 +2850,22 @@
         <v>8</v>
       </c>
       <c r="W29" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -2636,8 +2879,20 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2983,20 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,76 +3087,88 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="R32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>-200</v>
       </c>
       <c r="V32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="W32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="X32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Y32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
@@ -2910,10 +3189,22 @@
         <v>-100</v>
       </c>
       <c r="AF32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2921,91 +3212,103 @@
         <v>2100</v>
       </c>
       <c r="E33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F33" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H33" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I33" s="3">
         <v>1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="J33" s="3">
         <v>2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="K33" s="3">
         <v>2900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="L33" s="3">
         <v>2500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="M33" s="3">
         <v>2500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="N33" s="3">
         <v>2200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="O33" s="3">
         <v>900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
         <v>1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="U33" s="3">
         <v>600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="V33" s="3">
         <v>1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="W33" s="3">
         <v>800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AB33" s="3">
         <v>100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AC33" s="3">
         <v>700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AD33" s="3">
         <v>1300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AE33" s="3">
         <v>700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AF33" s="3">
         <v>1200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AG33" s="3">
         <v>1600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AH33" s="3">
         <v>1500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AI33" s="3">
         <v>600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AJ33" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,8 +3399,20 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3105,188 +3420,212 @@
         <v>2100</v>
       </c>
       <c r="E35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F35" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H35" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I35" s="3">
         <v>1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="J35" s="3">
         <v>2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="K35" s="3">
         <v>2900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="L35" s="3">
         <v>2500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="M35" s="3">
         <v>2500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="N35" s="3">
         <v>2200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="O35" s="3">
         <v>900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
         <v>1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="U35" s="3">
         <v>600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="V35" s="3">
         <v>1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="W35" s="3">
         <v>800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Z35" s="3">
         <v>900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="AA35" s="3">
         <v>100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AB35" s="3">
         <v>100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AC35" s="3">
         <v>700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AD35" s="3">
         <v>1300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AE35" s="3">
         <v>700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AF35" s="3">
         <v>1200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AG35" s="3">
         <v>1600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AH35" s="3">
         <v>1500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AI35" s="3">
         <v>600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AJ35" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45409</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45318</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45227</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45136</v>
+      </c>
+      <c r="H38" s="2">
         <v>45045</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>44954</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>44863</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>44772</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>44591</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>44499</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>44317</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>44226</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44044</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>43953</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="U38" s="2">
         <v>43832</v>
       </c>
-      <c r="R38" s="2">
+      <c r="V38" s="2">
         <v>43771</v>
       </c>
-      <c r="S38" s="2">
+      <c r="W38" s="2">
         <v>43680</v>
       </c>
-      <c r="T38" s="2">
+      <c r="X38" s="2">
         <v>43582</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Y38" s="2">
         <v>43491</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <v>43400</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AA38" s="2">
         <v>43309</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AB38" s="2">
         <v>43218</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AC38" s="2">
         <v>43127</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AD38" s="2">
         <v>43036</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AE38" s="2">
         <v>42945</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AF38" s="2">
         <v>42854</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AG38" s="2">
         <v>42763</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AH38" s="2">
         <v>42672</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AI38" s="2">
         <v>42581</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AJ38" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3658,12 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,180 +3696,196 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F41" s="3">
+        <v>24000</v>
+      </c>
+      <c r="G41" s="3">
+        <v>18300</v>
+      </c>
+      <c r="H41" s="3">
         <v>11100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>15400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>13300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>15300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>22400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>15100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>20700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>23500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>23000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>24700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>19100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>21000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="T41" s="3">
         <v>23200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="U41" s="3">
         <v>17300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="V41" s="3">
         <v>13600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="W41" s="3">
         <v>12800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>20400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Y41" s="3">
         <v>21200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>19200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AA41" s="3">
         <v>27600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AB41" s="3">
         <v>33900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AC41" s="3">
         <v>32300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AD41" s="3">
         <v>29200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AE41" s="3">
         <v>28100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AF41" s="3">
         <v>28100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AG41" s="3">
         <v>23400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AH41" s="3">
         <v>16600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AI41" s="3">
         <v>15700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AJ41" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>30200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>24100</v>
+      </c>
+      <c r="G42" s="3">
+        <v>21500</v>
+      </c>
+      <c r="H42" s="3">
         <v>18400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="I42" s="3">
         <v>10700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="J42" s="3">
         <v>10400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="K42" s="3">
         <v>10500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="L42" s="3">
         <v>8700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>6500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="N42" s="3">
         <v>6500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>8600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
         <v>10600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="Q42" s="3">
         <v>9300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="R42" s="3">
         <v>14200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="S42" s="3">
         <v>13900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="T42" s="3">
         <v>2700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="U42" s="3">
         <v>7200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="V42" s="3">
         <v>10900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="W42" s="3">
         <v>13200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="X42" s="3">
         <v>12100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="Y42" s="3">
         <v>9500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="Z42" s="3">
         <v>7800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="AA42" s="3">
         <v>2200</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>500</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>500</v>
-      </c>
-      <c r="AA42" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>400</v>
-      </c>
-      <c r="AC42" s="3">
-        <v>400</v>
       </c>
       <c r="AD42" s="3">
         <v>500</v>
@@ -3535,194 +3894,230 @@
         <v>500</v>
       </c>
       <c r="AF42" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH42" s="3">
         <v>500</v>
       </c>
+      <c r="AI42" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>16300</v>
+      </c>
+      <c r="F43" s="3">
+        <v>19400</v>
+      </c>
+      <c r="G43" s="3">
+        <v>20300</v>
+      </c>
+      <c r="H43" s="3">
         <v>21200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>19900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>23600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>26100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>21400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>29800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>23500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>16400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>16500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>14100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>13600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>9000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="T43" s="3">
         <v>13100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="U43" s="3">
         <v>14600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="V43" s="3">
         <v>14200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="W43" s="3">
         <v>13400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="X43" s="3">
         <v>10300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="Y43" s="3">
         <v>12400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z43" s="3">
         <v>14500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="AA43" s="3">
         <v>11800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AB43" s="3">
         <v>11000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AC43" s="3">
         <v>12800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AD43" s="3">
         <v>13900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AE43" s="3">
         <v>25000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AF43" s="3">
         <v>12300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AG43" s="3">
         <v>14500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AH43" s="3">
         <v>15400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AI43" s="3">
         <v>13600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AJ43" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>19800</v>
+      </c>
+      <c r="F44" s="3">
+        <v>18000</v>
+      </c>
+      <c r="G44" s="3">
+        <v>21900</v>
+      </c>
+      <c r="H44" s="3">
         <v>26600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="I44" s="3">
         <v>29700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>31500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>24500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>18400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>16800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>15600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>14300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>12400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>13700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="R44" s="3">
         <v>15300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="S44" s="3">
         <v>18300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="T44" s="3">
         <v>18100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="U44" s="3">
         <v>19500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="V44" s="3">
         <v>19800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="W44" s="3">
         <v>19800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="X44" s="3">
         <v>16100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="Y44" s="3">
         <v>15500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Z44" s="3">
         <v>17900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="AA44" s="3">
         <v>18400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="AB44" s="3">
         <v>14000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AC44" s="3">
         <v>13300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AD44" s="3">
         <v>17400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AE44" s="3">
         <v>18300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AF44" s="3">
         <v>18900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AG44" s="3">
         <v>19600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AH44" s="3">
         <v>24900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AI44" s="3">
         <v>55900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AJ44" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3730,10 +4125,10 @@
         <v>400</v>
       </c>
       <c r="E45" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F45" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G45" s="3">
         <v>300</v>
@@ -3742,355 +4137,403 @@
         <v>400</v>
       </c>
       <c r="I45" s="3">
+        <v>500</v>
+      </c>
+      <c r="J45" s="3">
         <v>600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>700</v>
       </c>
       <c r="K45" s="3">
         <v>300</v>
       </c>
       <c r="L45" s="3">
+        <v>400</v>
+      </c>
+      <c r="M45" s="3">
+        <v>600</v>
+      </c>
+      <c r="N45" s="3">
+        <v>700</v>
+      </c>
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>600</v>
-      </c>
-      <c r="R45" s="3">
-        <v>800</v>
-      </c>
-      <c r="S45" s="3">
-        <v>600</v>
       </c>
       <c r="T45" s="3">
         <v>400</v>
       </c>
       <c r="U45" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="V45" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="W45" s="3">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="X45" s="3">
         <v>400</v>
       </c>
       <c r="Y45" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AD45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AE45" s="3">
         <v>2200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AF45" s="3">
         <v>300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AG45" s="3">
         <v>400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AH45" s="3">
         <v>500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AI45" s="3">
         <v>2600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AJ45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>85200</v>
+      </c>
+      <c r="F46" s="3">
+        <v>86200</v>
+      </c>
+      <c r="G46" s="3">
+        <v>82300</v>
+      </c>
+      <c r="H46" s="3">
         <v>77700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>76100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>79500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>76800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>71200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>68700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>67000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>63100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>62900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>62100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>62700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>63000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="T46" s="3">
         <v>57500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="U46" s="3">
         <v>59200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="V46" s="3">
         <v>59300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="W46" s="3">
         <v>59800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="X46" s="3">
         <v>59300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="Y46" s="3">
         <v>59100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="3">
         <v>59800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="AA46" s="3">
         <v>60200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="AB46" s="3">
         <v>59400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AC46" s="3">
         <v>59200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AD46" s="3">
         <v>61500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AE46" s="3">
         <v>60000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AF46" s="3">
         <v>60000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AG46" s="3">
         <v>58300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AH46" s="3">
         <v>58000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AI46" s="3">
         <v>58200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AJ46" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E47" s="3">
-        <v>4000</v>
+        <v>2800</v>
       </c>
       <c r="F47" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="G47" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="H47" s="3">
         <v>4000</v>
       </c>
       <c r="I47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M47" s="3">
         <v>4100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>4100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>4300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>3200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>3200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>3200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>3800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="T47" s="3">
         <v>7700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="U47" s="3">
         <v>8000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="V47" s="3">
         <v>7900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="W47" s="3">
         <v>7800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="X47" s="3">
         <v>7800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="Y47" s="3">
         <v>7600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="Z47" s="3">
         <v>7600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="AA47" s="3">
         <v>7700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="AB47" s="3">
         <v>7600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AC47" s="3">
         <v>7700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AD47" s="3">
         <v>7500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AE47" s="3">
         <v>7400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AF47" s="3">
         <v>7200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AG47" s="3">
         <v>7200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AH47" s="3">
         <v>7200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AI47" s="3">
         <v>7100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AJ47" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5100</v>
+        <v>7200</v>
       </c>
       <c r="E48" s="3">
-        <v>5200</v>
+        <v>6900</v>
       </c>
       <c r="F48" s="3">
-        <v>5300</v>
+        <v>7100</v>
       </c>
       <c r="G48" s="3">
-        <v>5200</v>
+        <v>7300</v>
       </c>
       <c r="H48" s="3">
         <v>5100</v>
       </c>
       <c r="I48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="L48" s="3">
         <v>5100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N48" s="3">
         <v>5200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>5400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>5500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>5700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>5900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>6100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="T48" s="3">
         <v>6200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="U48" s="3">
         <v>6300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="V48" s="3">
         <v>6400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="W48" s="3">
         <v>6600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="X48" s="3">
         <v>6700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Y48" s="3">
         <v>6800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>7100</v>
-      </c>
-      <c r="W48" s="3">
-        <v>7400</v>
-      </c>
-      <c r="X48" s="3">
-        <v>7200</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>7400</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>7600</v>
       </c>
       <c r="AA48" s="3">
         <v>7400</v>
       </c>
       <c r="AB48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AD48" s="3">
         <v>7600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AG48" s="3">
         <v>7800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AH48" s="3">
         <v>7900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AI48" s="3">
         <v>8100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AJ48" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4181,8 +4624,20 @@
       <c r="AF49" s="3">
         <v>2800</v>
       </c>
+      <c r="AG49" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AJ49" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4728,20 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,22 +4832,34 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>2300</v>
@@ -4425,10 +4904,10 @@
         <v>2300</v>
       </c>
       <c r="V52" s="3">
-        <v>3400</v>
+        <v>2300</v>
       </c>
       <c r="W52" s="3">
-        <v>3400</v>
+        <v>2300</v>
       </c>
       <c r="X52" s="3">
         <v>2300</v>
@@ -4437,10 +4916,10 @@
         <v>2300</v>
       </c>
       <c r="Z52" s="3">
-        <v>2300</v>
+        <v>3400</v>
       </c>
       <c r="AA52" s="3">
-        <v>2300</v>
+        <v>3400</v>
       </c>
       <c r="AB52" s="3">
         <v>2300</v>
@@ -4457,8 +4936,20 @@
       <c r="AF52" s="3">
         <v>2300</v>
       </c>
+      <c r="AG52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AJ52" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,100 +5040,124 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>98900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>97800</v>
+      </c>
+      <c r="F54" s="3">
+        <v>99100</v>
+      </c>
+      <c r="G54" s="3">
+        <v>95500</v>
+      </c>
+      <c r="H54" s="3">
         <v>92000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>90500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>93900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>91000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>85400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>83000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>81400</v>
-      </c>
-      <c r="K54" s="3">
-        <v>77900</v>
-      </c>
-      <c r="L54" s="3">
-        <v>76700</v>
-      </c>
-      <c r="M54" s="3">
-        <v>76200</v>
-      </c>
-      <c r="N54" s="3">
-        <v>76900</v>
       </c>
       <c r="O54" s="3">
         <v>77900</v>
       </c>
       <c r="P54" s="3">
+        <v>76700</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>76200</v>
+      </c>
+      <c r="R54" s="3">
+        <v>76900</v>
+      </c>
+      <c r="S54" s="3">
+        <v>77900</v>
+      </c>
+      <c r="T54" s="3">
         <v>76600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="U54" s="3">
         <v>78600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="V54" s="3">
         <v>78700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="W54" s="3">
         <v>79400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="X54" s="3">
         <v>78900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Y54" s="3">
         <v>78700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>80800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AA54" s="3">
         <v>80400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AB54" s="3">
         <v>79300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AC54" s="3">
         <v>79400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AD54" s="3">
         <v>81600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AE54" s="3">
         <v>80000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AF54" s="3">
         <v>80000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AG54" s="3">
         <v>78400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AH54" s="3">
         <v>78300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AI54" s="3">
         <v>78600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AJ54" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +5190,12 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,100 +5228,116 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>5200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>2800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>3100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>3200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>2200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="S57" s="3">
         <v>3900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="T57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="U57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="W57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="X57" s="3">
         <v>2500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="Y57" s="3">
         <v>2600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>2900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="AA57" s="3">
         <v>3000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="AB57" s="3">
         <v>2400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AC57" s="3">
         <v>2200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AD57" s="3">
         <v>2500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AE57" s="3">
         <v>2500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AF57" s="3">
         <v>3300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AG57" s="3">
         <v>2600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AH57" s="3">
         <v>3100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AI57" s="3">
         <v>4700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AJ57" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4893,192 +5428,228 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F59" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H59" s="3">
         <v>3500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>3400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>6100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>4600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>3400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>2900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>3500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>2400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>1900</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1500</v>
       </c>
       <c r="Q59" s="3">
         <v>1700</v>
       </c>
       <c r="R59" s="3">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="S59" s="3">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="T59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U59" s="3">
         <v>1700</v>
-      </c>
-      <c r="U59" s="3">
-        <v>1500</v>
       </c>
       <c r="V59" s="3">
         <v>2000</v>
       </c>
       <c r="W59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="X59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AB59" s="3">
         <v>1800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AC59" s="3">
         <v>1600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AD59" s="3">
         <v>3900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AE59" s="3">
         <v>4000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AF59" s="3">
         <v>2900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AG59" s="3">
         <v>2400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AH59" s="3">
         <v>3200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AI59" s="3">
         <v>3000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AJ59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F60" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G60" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H60" s="3">
         <v>6100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>6400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>10100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>9800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>6200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>6000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>6700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>5100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>3900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>4000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>4700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="S60" s="3">
         <v>5400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="T60" s="3">
         <v>2700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="U60" s="3">
         <v>3600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="V60" s="3">
         <v>4000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="W60" s="3">
         <v>5300</v>
-      </c>
-      <c r="T60" s="3">
-        <v>4200</v>
-      </c>
-      <c r="U60" s="3">
-        <v>4100</v>
-      </c>
-      <c r="V60" s="3">
-        <v>4900</v>
-      </c>
-      <c r="W60" s="3">
-        <v>4800</v>
       </c>
       <c r="X60" s="3">
         <v>4200</v>
       </c>
       <c r="Y60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AC60" s="3">
         <v>3800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AD60" s="3">
         <v>6400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AE60" s="3">
         <v>5800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AF60" s="3">
         <v>6200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AG60" s="3">
         <v>5000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AH60" s="3">
         <v>6200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AI60" s="3">
         <v>7700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AJ60" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5169,46 +5740,58 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
-      </c>
-      <c r="L62" s="3">
-        <v>700</v>
-      </c>
-      <c r="M62" s="3">
-        <v>700</v>
-      </c>
-      <c r="N62" s="3">
-        <v>700</v>
-      </c>
-      <c r="O62" s="3">
-        <v>700</v>
       </c>
       <c r="P62" s="3">
         <v>700</v>
@@ -5223,28 +5806,28 @@
         <v>700</v>
       </c>
       <c r="T62" s="3">
+        <v>700</v>
+      </c>
+      <c r="U62" s="3">
+        <v>700</v>
+      </c>
+      <c r="V62" s="3">
+        <v>700</v>
+      </c>
+      <c r="W62" s="3">
+        <v>700</v>
+      </c>
+      <c r="X62" s="3">
         <v>600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="Y62" s="3">
         <v>600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Z62" s="3">
         <v>1700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AA62" s="3">
         <v>1200</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>2300</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
@@ -5261,8 +5844,20 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5948,20 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +6052,20 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,100 +6156,124 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>9300</v>
+      </c>
+      <c r="G66" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H66" s="3">
         <v>6100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>6500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>10200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>9800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>6700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>6600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>7200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>5600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>4600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>4600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>5400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>6100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="T66" s="3">
         <v>3400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="U66" s="3">
         <v>4300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="V66" s="3">
         <v>4700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="W66" s="3">
         <v>6000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="X66" s="3">
         <v>4800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="Y66" s="3">
         <v>4700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>6600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AA66" s="3">
         <v>5400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AB66" s="3">
         <v>4200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AC66" s="3">
         <v>3800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AD66" s="3">
         <v>6400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AE66" s="3">
         <v>5800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AF66" s="3">
         <v>6200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AG66" s="3">
         <v>5000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AH66" s="3">
         <v>6200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AI66" s="3">
         <v>7700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AJ66" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +6306,12 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +6402,20 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6506,20 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6610,20 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,100 +6714,124 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>89200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>87500</v>
+      </c>
+      <c r="F72" s="3">
+        <v>87600</v>
+      </c>
+      <c r="G72" s="3">
+        <v>84700</v>
+      </c>
+      <c r="H72" s="3">
         <v>83600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>81800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>81500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>79000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>76400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>74200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>71900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>70000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>69900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>69300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>69200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>69500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="T72" s="3">
         <v>71100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="U72" s="3">
         <v>71900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="V72" s="3">
         <v>71700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="W72" s="3">
         <v>71000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="X72" s="3">
         <v>71800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>71700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>72000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="AA72" s="3">
         <v>72600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AB72" s="3">
         <v>72800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AC72" s="3">
         <v>73200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AD72" s="3">
         <v>72800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AE72" s="3">
         <v>71800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AF72" s="3">
         <v>71400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AG72" s="3">
         <v>71000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AH72" s="3">
         <v>69700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AI72" s="3">
         <v>68500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AJ72" s="3">
         <v>68200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6922,20 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +7026,20 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,100 +7130,124 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>89800</v>
+      </c>
+      <c r="F76" s="3">
+        <v>89800</v>
+      </c>
+      <c r="G76" s="3">
+        <v>86900</v>
+      </c>
+      <c r="H76" s="3">
         <v>85800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>84100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>83800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>81200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>78700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>76400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>74200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>72200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>72200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>71600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>71500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>71800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="T76" s="3">
         <v>73200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>74300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>74000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>73300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>74100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>74000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>74200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AA76" s="3">
         <v>75000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AB76" s="3">
         <v>75200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AC76" s="3">
         <v>75600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AD76" s="3">
         <v>75200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AE76" s="3">
         <v>74200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AF76" s="3">
         <v>73800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AG76" s="3">
         <v>73400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AH76" s="3">
         <v>72100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AI76" s="3">
         <v>70900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AJ76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,105 +7338,129 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45409</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45318</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45227</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45136</v>
+      </c>
+      <c r="H80" s="2">
         <v>45045</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>44954</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>44863</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>44772</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>44591</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>44499</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>44317</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>44226</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44044</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>43953</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="U80" s="2">
         <v>43832</v>
       </c>
-      <c r="R80" s="2">
+      <c r="V80" s="2">
         <v>43771</v>
       </c>
-      <c r="S80" s="2">
+      <c r="W80" s="2">
         <v>43680</v>
       </c>
-      <c r="T80" s="2">
+      <c r="X80" s="2">
         <v>43582</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Y80" s="2">
         <v>43491</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Z80" s="2">
         <v>43400</v>
       </c>
-      <c r="W80" s="2">
+      <c r="AA80" s="2">
         <v>43309</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AB80" s="2">
         <v>43218</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AC80" s="2">
         <v>43127</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AD80" s="2">
         <v>43036</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AE80" s="2">
         <v>42945</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AF80" s="2">
         <v>42854</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AG80" s="2">
         <v>42763</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AH80" s="2">
         <v>42672</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AI80" s="2">
         <v>42581</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AJ80" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6689,91 +7468,103 @@
         <v>2100</v>
       </c>
       <c r="E81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F81" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H81" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I81" s="3">
         <v>1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="J81" s="3">
         <v>2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="K81" s="3">
         <v>2900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="L81" s="3">
         <v>2500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="M81" s="3">
         <v>2500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="N81" s="3">
         <v>2200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="O81" s="3">
         <v>900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
         <v>1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="U81" s="3">
         <v>600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="V81" s="3">
         <v>1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="W81" s="3">
         <v>800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AA81" s="3">
         <v>100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AB81" s="3">
         <v>100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AC81" s="3">
         <v>700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AD81" s="3">
         <v>1300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AE81" s="3">
         <v>700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AF81" s="3">
         <v>1200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AG81" s="3">
         <v>1600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AH81" s="3">
         <v>1500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AI81" s="3">
         <v>600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AJ81" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,8 +7597,12 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6898,8 +7693,20 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7797,20 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7901,20 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +8005,20 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +8109,20 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +8213,124 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F89" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G89" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H89" s="3">
         <v>4000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>3800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>-4500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>10400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>-5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>-4800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="R89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="S89" s="3">
         <v>5200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="T89" s="3">
         <v>2000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="U89" s="3">
         <v>500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="V89" s="3">
         <v>-1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="W89" s="3">
         <v>-4700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="X89" s="3">
         <v>2200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="Y89" s="3">
         <v>4100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Z89" s="3">
         <v>-1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="AA89" s="3">
         <v>-3300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="AB89" s="3">
         <v>1700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AC89" s="3">
         <v>3800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AD89" s="3">
         <v>2000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AE89" s="3">
         <v>600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AF89" s="3">
         <v>5600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AG89" s="3">
         <v>7100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AH89" s="3">
         <v>1500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AI89" s="3">
         <v>800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AJ89" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,37 +8363,41 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -7523,16 +8406,16 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7553,31 +8436,43 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
       <c r="AA91" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AB91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="3">
         <v>-200</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AJ91" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +8563,20 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,100 +8667,124 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="H94" s="3">
         <v>-7900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>-2200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>2200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>4900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="R94" s="3">
         <v>100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="S94" s="3">
         <v>-7100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="T94" s="3">
         <v>4300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="U94" s="3">
         <v>3600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="V94" s="3">
         <v>2100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="W94" s="3">
         <v>-1400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="X94" s="3">
         <v>-2600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="Y94" s="3">
         <v>-1800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="Z94" s="3">
         <v>-5700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="AA94" s="3">
         <v>-2700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="AB94" s="3">
         <v>400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AC94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AD94" s="3">
         <v>-500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AE94" s="3">
         <v>-400</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AH94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AI94" s="3">
         <v>-700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AJ94" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8817,12 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7895,7 +8830,7 @@
         <v>-300</v>
       </c>
       <c r="E96" s="3">
-        <v>-1400</v>
+        <v>-1700</v>
       </c>
       <c r="F96" s="3">
         <v>-300</v>
@@ -7907,7 +8842,7 @@
         <v>-300</v>
       </c>
       <c r="I96" s="3">
-        <v>-300</v>
+        <v>-1400</v>
       </c>
       <c r="J96" s="3">
         <v>-300</v>
@@ -7946,7 +8881,7 @@
         <v>-300</v>
       </c>
       <c r="V96" s="3">
-        <v>-1500</v>
+        <v>-300</v>
       </c>
       <c r="W96" s="3">
         <v>-300</v>
@@ -7958,7 +8893,7 @@
         <v>-300</v>
       </c>
       <c r="Z96" s="3">
-        <v>-300</v>
+        <v>-1500</v>
       </c>
       <c r="AA96" s="3">
         <v>-300</v>
@@ -7978,8 +8913,20 @@
       <c r="AF96" s="3">
         <v>-300</v>
       </c>
+      <c r="AG96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +9017,20 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +9121,20 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,8 +9225,20 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8263,7 +9246,7 @@
         <v>-300</v>
       </c>
       <c r="E100" s="3">
-        <v>-1400</v>
+        <v>-1700</v>
       </c>
       <c r="F100" s="3">
         <v>-300</v>
@@ -8275,64 +9258,64 @@
         <v>-300</v>
       </c>
       <c r="I100" s="3">
-        <v>-300</v>
+        <v>-1400</v>
       </c>
       <c r="J100" s="3">
         <v>-300</v>
       </c>
       <c r="K100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>-600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="T100" s="3">
         <v>-400</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-300</v>
       </c>
       <c r="U100" s="3">
         <v>-300</v>
       </c>
       <c r="V100" s="3">
-        <v>-1500</v>
+        <v>-300</v>
       </c>
       <c r="W100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="X100" s="3">
         <v>-300</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-400</v>
       </c>
       <c r="Y100" s="3">
         <v>-300</v>
       </c>
       <c r="Z100" s="3">
-        <v>-300</v>
+        <v>-1500</v>
       </c>
       <c r="AA100" s="3">
         <v>-300</v>
       </c>
       <c r="AB100" s="3">
-        <v>-900</v>
+        <v>-400</v>
       </c>
       <c r="AC100" s="3">
         <v>-300</v>
@@ -8344,10 +9327,22 @@
         <v>-300</v>
       </c>
       <c r="AF100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8438,96 +9433,120 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F102" s="3">
+        <v>5700</v>
+      </c>
+      <c r="G102" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H102" s="3">
         <v>-4300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>-7100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>7300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>-5600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>-1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>5500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>-2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="T102" s="3">
         <v>5900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="U102" s="3">
         <v>3700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="V102" s="3">
         <v>800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="W102" s="3">
         <v>-7600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="X102" s="3">
         <v>-800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="Y102" s="3">
         <v>1900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Z102" s="3">
         <v>-8400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="AA102" s="3">
         <v>-6300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="AB102" s="3">
         <v>1600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AC102" s="3">
         <v>3100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AD102" s="3">
         <v>1100</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>4700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AG102" s="3">
         <v>6800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AH102" s="3">
         <v>1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AI102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AJ102" s="3">
         <v>3400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCRAA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCRAA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>MCRAA</t>
   </si>
@@ -656,468 +656,481 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E7" s="2">
         <v>45409</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45318</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45136</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45045</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44954</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44863</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44772</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44591</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44499</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44317</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44226</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44044</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43953</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43832</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43771</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43680</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43582</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43491</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43400</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43309</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43218</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43127</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43036</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42945</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42854</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42763</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42672</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42581</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>29400</v>
-      </c>
-      <c r="E8" s="3">
-        <v>25800</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
+        <v>33800</v>
+      </c>
+      <c r="L8" s="3">
+        <v>33000</v>
+      </c>
+      <c r="M8" s="3">
         <v>32800</v>
       </c>
-      <c r="G8" s="3">
-        <v>28600</v>
-      </c>
-      <c r="H8" s="3">
-        <v>31500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>30800</v>
-      </c>
-      <c r="J8" s="3">
-        <v>33800</v>
-      </c>
-      <c r="K8" s="3">
-        <v>33000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>32800</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>31400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>27600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>20600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>22400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>22200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>24100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>28100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>29900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>21400</v>
-      </c>
-      <c r="E9" s="3">
-        <v>18800</v>
-      </c>
-      <c r="F9" s="3">
-        <v>22900</v>
-      </c>
-      <c r="G9" s="3">
-        <v>21800</v>
-      </c>
-      <c r="H9" s="3">
-        <v>22800</v>
-      </c>
-      <c r="I9" s="3">
-        <v>22800</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>23500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>23400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>23100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>11600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15300</v>
-      </c>
-      <c r="V9" s="3">
-        <v>17000</v>
       </c>
       <c r="W9" s="3">
         <v>17000</v>
       </c>
       <c r="X9" s="3">
+        <v>17000</v>
+      </c>
+      <c r="Y9" s="3">
         <v>14400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>15300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>11300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>16200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>17200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>18300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>20700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>22500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
+        <v>10300</v>
+      </c>
+      <c r="L10" s="3">
+        <v>9600</v>
+      </c>
+      <c r="M10" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N10" s="3">
+        <v>9100</v>
+      </c>
+      <c r="O10" s="3">
         <v>8000</v>
       </c>
-      <c r="E10" s="3">
-        <v>7000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>9900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>8700</v>
-      </c>
-      <c r="I10" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>10300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>9600</v>
-      </c>
-      <c r="L10" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M10" s="3">
-        <v>9100</v>
-      </c>
-      <c r="N10" s="3">
-        <v>8000</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>6200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5800</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>7400</v>
       </c>
       <c r="AH10" s="3">
         <v>7400</v>
       </c>
       <c r="AI10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1154,8 +1167,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1258,8 +1272,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1362,31 +1379,34 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1466,31 +1486,34 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1570,8 +1593,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1605,216 +1631,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>27200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>24400</v>
-      </c>
-      <c r="F17" s="3">
-        <v>28900</v>
-      </c>
-      <c r="G17" s="3">
-        <v>27300</v>
-      </c>
-      <c r="H17" s="3">
-        <v>28700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>28900</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>29500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>20700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>19500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>15200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>20400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>22300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>25500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>27500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>22500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>24100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>2200</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>3900</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>400</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
       <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>1100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1851,64 +1884,65 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>400</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>200</v>
       </c>
       <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>200</v>
       </c>
       <c r="V20" s="3">
         <v>200</v>
@@ -1923,7 +1957,7 @@
         <v>200</v>
       </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
@@ -1953,10 +1987,13 @@
         <v>100</v>
       </c>
       <c r="AJ20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2059,31 +2096,34 @@
       <c r="AJ21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2100,8 +2140,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
@@ -2109,11 +2149,11 @@
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
@@ -2121,11 +2161,11 @@
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
@@ -2133,11 +2173,11 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
@@ -2145,11 +2185,11 @@
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="3" t="s">
-        <v>8</v>
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
       </c>
       <c r="AG22" s="3" t="s">
         <v>8</v>
@@ -2157,222 +2197,231 @@
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="3" t="s">
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>2800</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>4100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L24" s="3">
+        <v>500</v>
+      </c>
+      <c r="M24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>900</v>
+      </c>
+      <c r="O24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
-        <v>600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>700</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="P24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>500</v>
+      </c>
+      <c r="R24" s="3">
+        <v>300</v>
+      </c>
+      <c r="S24" s="3">
+        <v>200</v>
+      </c>
+      <c r="T24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V24" s="3">
+        <v>300</v>
+      </c>
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
-        <v>900</v>
-      </c>
-      <c r="I24" s="3">
-        <v>600</v>
-      </c>
-      <c r="J24" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>500</v>
-      </c>
-      <c r="L24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>900</v>
-      </c>
-      <c r="N24" s="3">
-        <v>800</v>
-      </c>
-      <c r="O24" s="3">
-        <v>100</v>
-      </c>
-      <c r="P24" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>300</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
-      </c>
-      <c r="S24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="T24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U24" s="3">
-        <v>300</v>
-      </c>
-      <c r="V24" s="3">
-        <v>400</v>
-      </c>
-      <c r="W24" s="3">
-        <v>200</v>
-      </c>
-      <c r="X24" s="3">
-        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>100</v>
       </c>
       <c r="Z24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>800</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>1000</v>
       </c>
       <c r="AH24" s="3">
         <v>1000</v>
       </c>
       <c r="AI24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2475,216 +2524,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>2100</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J26" s="3">
-        <v>2900</v>
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K26" s="3">
         <v>2900</v>
       </c>
       <c r="L26" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="M26" s="3">
         <v>2500</v>
       </c>
       <c r="N26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O26" s="3">
         <v>2200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>2100</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F27" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>2900</v>
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K27" s="3">
         <v>2900</v>
       </c>
       <c r="L27" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="M27" s="3">
         <v>2500</v>
       </c>
       <c r="N27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O27" s="3">
         <v>2200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2787,31 +2845,34 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2840,8 +2901,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2849,11 +2910,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2861,14 +2922,14 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>400</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -2891,8 +2952,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2995,8 +3059,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3099,64 +3166,67 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-200</v>
       </c>
       <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-200</v>
       </c>
       <c r="V32" s="3">
         <v>-200</v>
@@ -3171,7 +3241,7 @@
         <v>-200</v>
       </c>
       <c r="Z32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
@@ -3201,114 +3271,120 @@
         <v>-100</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>2100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F33" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>2900</v>
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K33" s="3">
         <v>2900</v>
       </c>
       <c r="L33" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="M33" s="3">
         <v>2500</v>
       </c>
       <c r="N33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O33" s="3">
         <v>2200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>900</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>100</v>
       </c>
       <c r="AB33" s="3">
         <v>100</v>
       </c>
       <c r="AC33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD33" s="3">
         <v>700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3411,221 +3487,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>2100</v>
-      </c>
-      <c r="E35" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F35" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>2900</v>
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K35" s="3">
         <v>2900</v>
       </c>
       <c r="L35" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="M35" s="3">
         <v>2500</v>
       </c>
       <c r="N35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O35" s="3">
         <v>2200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>900</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>100</v>
       </c>
       <c r="AB35" s="3">
         <v>100</v>
       </c>
       <c r="AC35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD35" s="3">
         <v>700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E38" s="2">
         <v>45409</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45318</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45136</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45045</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44954</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44863</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44772</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44591</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44499</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44317</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44226</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44044</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43953</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43832</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43771</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43680</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43582</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43491</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43400</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43309</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43218</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43127</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43036</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42945</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42854</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42763</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42672</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42581</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3662,8 +3747,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3700,192 +3786,196 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E41" s="3">
         <v>19600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>24000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>23200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>17300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>13600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>21200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>27600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>33900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>32300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>29200</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>28100</v>
       </c>
       <c r="AF41" s="3">
         <v>28100</v>
       </c>
       <c r="AG41" s="3">
+        <v>28100</v>
+      </c>
+      <c r="AH41" s="3">
         <v>23400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>16600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>15700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E42" s="3">
         <v>28000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>30200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>24100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>21500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>18400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8700</v>
-      </c>
-      <c r="M42" s="3">
-        <v>6500</v>
       </c>
       <c r="N42" s="3">
         <v>6500</v>
       </c>
       <c r="O42" s="3">
+        <v>6500</v>
+      </c>
+      <c r="P42" s="3">
         <v>8600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>9300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>14200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>13900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>7200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>10900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>13200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>12100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>7800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2200</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
       <c r="AC42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AD42" s="3">
         <v>500</v>
@@ -3894,13 +3984,13 @@
         <v>500</v>
       </c>
       <c r="AF42" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AG42" s="3">
         <v>400</v>
       </c>
       <c r="AH42" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AI42" s="3">
         <v>500</v>
@@ -3908,447 +3998,462 @@
       <c r="AJ42" s="3">
         <v>500</v>
       </c>
+      <c r="AK42" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E43" s="3">
         <v>17400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>21400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>12400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>14500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>11800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>11000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>12800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>13900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>25000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>12300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>14500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>15400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>13600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E44" s="3">
         <v>20500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>19800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>21900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>26600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>29700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>31500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>24500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>15600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>15300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>18300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>18100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>19500</v>
-      </c>
-      <c r="V44" s="3">
-        <v>19800</v>
       </c>
       <c r="W44" s="3">
         <v>19800</v>
       </c>
       <c r="X44" s="3">
+        <v>19800</v>
+      </c>
+      <c r="Y44" s="3">
         <v>16100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>15500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>17900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>14000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>13300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>17400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>18300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>18900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>19600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>24900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>55900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
+        <v>600</v>
+      </c>
+      <c r="L45" s="3">
+        <v>300</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>400</v>
-      </c>
-      <c r="M45" s="3">
-        <v>600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>700</v>
-      </c>
-      <c r="O45" s="3">
-        <v>300</v>
       </c>
       <c r="P45" s="3">
         <v>300</v>
       </c>
       <c r="Q45" s="3">
+        <v>300</v>
+      </c>
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
-      </c>
-      <c r="X45" s="3">
-        <v>400</v>
       </c>
       <c r="Y45" s="3">
         <v>400</v>
       </c>
       <c r="Z45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA45" s="3">
         <v>500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E46" s="3">
         <v>85800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>85200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>86200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>82300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>77700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>76100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>79500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>76800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>71200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>68700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>67000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>63100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>62900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>62100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>62700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>63000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>57500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>59200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>59300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>59800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>59300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>59100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>59800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>60200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>59400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>59200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>61500</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>60000</v>
       </c>
       <c r="AF46" s="3">
         <v>60000</v>
       </c>
       <c r="AG46" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AH46" s="3">
         <v>58300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>58000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>58200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2800</v>
-      </c>
-      <c r="F47" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>4000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>4000</v>
+        <v>11100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>4000</v>
@@ -4357,16 +4462,16 @@
         <v>4000</v>
       </c>
       <c r="M47" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="N47" s="3">
         <v>4100</v>
       </c>
       <c r="O47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="P47" s="3">
         <v>4300</v>
-      </c>
-      <c r="P47" s="3">
-        <v>3200</v>
       </c>
       <c r="Q47" s="3">
         <v>3200</v>
@@ -4375,46 +4480,46 @@
         <v>3200</v>
       </c>
       <c r="S47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="T47" s="3">
         <v>3800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7900</v>
-      </c>
-      <c r="W47" s="3">
-        <v>7800</v>
       </c>
       <c r="X47" s="3">
         <v>7800</v>
       </c>
       <c r="Y47" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="Z47" s="3">
         <v>7600</v>
       </c>
       <c r="AA47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AB47" s="3">
         <v>7700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AF47" s="3">
-        <v>7200</v>
       </c>
       <c r="AG47" s="3">
         <v>7200</v>
@@ -4423,117 +4528,123 @@
         <v>7200</v>
       </c>
       <c r="AI47" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="AJ47" s="3">
         <v>7100</v>
       </c>
+      <c r="AK47" s="3">
+        <v>7100</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E48" s="3">
         <v>7200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>5100</v>
       </c>
       <c r="M48" s="3">
         <v>5100</v>
       </c>
       <c r="N48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="O48" s="3">
         <v>5200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4636,8 +4747,11 @@
       <c r="AJ49" s="3">
         <v>2800</v>
       </c>
+      <c r="AK49" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4740,8 +4854,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4844,31 +4961,34 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H52" s="3">
-        <v>2300</v>
+        <v>3100</v>
       </c>
       <c r="I52" s="3">
-        <v>2300</v>
+        <v>5300</v>
       </c>
       <c r="J52" s="3">
-        <v>2300</v>
+        <v>5300</v>
       </c>
       <c r="K52" s="3">
         <v>2300</v>
@@ -4916,13 +5036,13 @@
         <v>2300</v>
       </c>
       <c r="Z52" s="3">
-        <v>3400</v>
+        <v>2300</v>
       </c>
       <c r="AA52" s="3">
         <v>3400</v>
       </c>
       <c r="AB52" s="3">
-        <v>2300</v>
+        <v>3400</v>
       </c>
       <c r="AC52" s="3">
         <v>2300</v>
@@ -4948,8 +5068,11 @@
       <c r="AJ52" s="3">
         <v>2300</v>
       </c>
+      <c r="AK52" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5052,112 +5175,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>106500</v>
+      </c>
+      <c r="E54" s="3">
         <v>98900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>97800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>99100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>95500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>92000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>90500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>93900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>91000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>85400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>83000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>81400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>77900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>76700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>76200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>76900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>77900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>76600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>78600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>78700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>79400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>78900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>78700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>80800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>80400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>79300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>79400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>81600</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>80000</v>
       </c>
       <c r="AF54" s="3">
         <v>80000</v>
       </c>
       <c r="AG54" s="3">
+        <v>80000</v>
+      </c>
+      <c r="AH54" s="3">
         <v>78400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>78300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>78600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5194,8 +5323,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5232,129 +5362,133 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2200</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>2500</v>
       </c>
       <c r="AE57" s="3">
         <v>2500</v>
       </c>
       <c r="AF57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AG57" s="3">
         <v>3300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -5440,233 +5574,242 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3100</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H59" s="3">
+        <v>900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>6100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>4600</v>
+      </c>
+      <c r="M59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N59" s="3">
         <v>2900</v>
       </c>
-      <c r="F59" s="3">
-        <v>4600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="O59" s="3">
         <v>3500</v>
       </c>
-      <c r="I59" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>6100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>4600</v>
-      </c>
-      <c r="L59" s="3">
-        <v>3400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>2900</v>
-      </c>
-      <c r="N59" s="3">
-        <v>3500</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1800</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1500</v>
       </c>
       <c r="T59" s="3">
         <v>1500</v>
       </c>
       <c r="U59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>1800</v>
       </c>
       <c r="AB59" s="3">
         <v>1800</v>
       </c>
       <c r="AC59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AD59" s="3">
         <v>1600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E60" s="3">
         <v>5700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -5752,37 +5895,40 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
       </c>
       <c r="L62" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M62" s="3">
         <v>500</v>
@@ -5794,7 +5940,7 @@
         <v>500</v>
       </c>
       <c r="P62" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="Q62" s="3">
         <v>700</v>
@@ -5818,46 +5964,49 @@
         <v>700</v>
       </c>
       <c r="X62" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Y62" s="3">
         <v>600</v>
       </c>
       <c r="Z62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA62" s="3">
         <v>1700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1200</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF62" s="3">
         <v>2300</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ62" s="3" t="s">
+      <c r="AK62" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5960,8 +6109,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6064,8 +6216,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6168,112 +6323,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E66" s="3">
         <v>7400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5600</v>
-      </c>
-      <c r="P66" s="3">
-        <v>4600</v>
       </c>
       <c r="Q66" s="3">
         <v>4600</v>
       </c>
       <c r="R66" s="3">
+        <v>4600</v>
+      </c>
+      <c r="S66" s="3">
         <v>5400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6310,8 +6471,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6414,8 +6576,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6518,8 +6683,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6622,8 +6790,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6726,112 +6897,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>94800</v>
+      </c>
+      <c r="E72" s="3">
         <v>89200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>87500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>87600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>84700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>83600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>81800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>81500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>79000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>76400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>74200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>71900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>70000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>69900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>69300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>69200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>69500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>71100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>71900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>71700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>71000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>71800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>71700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>72000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>72600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>72800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>73200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>72800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>71800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>71400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>71000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>69700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>68500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>68200</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6934,8 +7111,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7038,8 +7218,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7142,112 +7325,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>97100</v>
+      </c>
+      <c r="E76" s="3">
         <v>91500</v>
-      </c>
-      <c r="E76" s="3">
-        <v>89800</v>
       </c>
       <c r="F76" s="3">
         <v>89800</v>
       </c>
       <c r="G76" s="3">
+        <v>89800</v>
+      </c>
+      <c r="H76" s="3">
         <v>86900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>85800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>84100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>83800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>81200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>78700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>76400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>74200</v>
-      </c>
-      <c r="O76" s="3">
-        <v>72200</v>
       </c>
       <c r="P76" s="3">
         <v>72200</v>
       </c>
       <c r="Q76" s="3">
+        <v>72200</v>
+      </c>
+      <c r="R76" s="3">
         <v>71600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>71500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>71800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>73200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>74300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>74000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>73300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>74100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>74000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>74200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>75000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>75200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>75600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>75200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>74200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>73800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>73400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>72100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>70900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7350,221 +7539,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E80" s="2">
         <v>45409</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45318</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45136</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45045</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44954</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44863</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44772</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44591</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44499</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44317</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44226</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44044</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43953</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43832</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43771</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43680</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43582</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43491</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43400</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43309</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43218</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43127</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43036</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42945</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42854</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42763</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42672</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42581</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>2100</v>
-      </c>
-      <c r="E81" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F81" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>2900</v>
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K81" s="3">
         <v>2900</v>
       </c>
       <c r="L81" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="M81" s="3">
         <v>2500</v>
       </c>
       <c r="N81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O81" s="3">
         <v>2200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>900</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>100</v>
       </c>
       <c r="AB81" s="3">
         <v>100</v>
       </c>
       <c r="AC81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD81" s="3">
         <v>700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7601,31 +7799,32 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>1000</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7705,8 +7904,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7809,8 +8011,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7913,8 +8118,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8017,8 +8225,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8121,8 +8332,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8225,112 +8439,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8367,40 +8587,41 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-300</v>
       </c>
       <c r="L91" s="3">
         <v>-300</v>
       </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
@@ -8409,16 +8630,16 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -8448,31 +8669,34 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8575,8 +8799,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8679,112 +8906,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E94" s="3">
         <v>1700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2800</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>2200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>4900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>4300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>3600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-400</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8821,31 +9054,32 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="E96" s="3">
-        <v>-1700</v>
+        <v>300</v>
       </c>
       <c r="F96" s="3">
-        <v>-300</v>
+        <v>1700</v>
       </c>
       <c r="G96" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="H96" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="I96" s="3">
-        <v>-1400</v>
+        <v>300</v>
       </c>
       <c r="J96" s="3">
-        <v>-300</v>
+        <v>1400</v>
       </c>
       <c r="K96" s="3">
         <v>-300</v>
@@ -8893,10 +9127,10 @@
         <v>-300</v>
       </c>
       <c r="Z96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-300</v>
       </c>
       <c r="AB96" s="3">
         <v>-300</v>
@@ -8925,8 +9159,11 @@
       <c r="AJ96" s="3">
         <v>-300</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9029,8 +9266,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9133,8 +9373,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9237,8 +9480,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9246,10 +9492,10 @@
         <v>-300</v>
       </c>
       <c r="E100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-300</v>
       </c>
       <c r="G100" s="3">
         <v>-300</v>
@@ -9258,10 +9504,10 @@
         <v>-300</v>
       </c>
       <c r="I100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J100" s="3">
         <v>-1400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-300</v>
       </c>
       <c r="K100" s="3">
         <v>-300</v>
@@ -9276,49 +9522,49 @@
         <v>-300</v>
       </c>
       <c r="O100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P100" s="3">
         <v>-800</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-600</v>
       </c>
       <c r="Q100" s="3">
         <v>-600</v>
       </c>
       <c r="R100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S100" s="3">
         <v>-800</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-400</v>
       </c>
       <c r="T100" s="3">
         <v>-400</v>
       </c>
       <c r="U100" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="V100" s="3">
         <v>-300</v>
       </c>
       <c r="W100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X100" s="3">
         <v>-1600</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-300</v>
       </c>
       <c r="Y100" s="3">
         <v>-300</v>
       </c>
       <c r="Z100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-400</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>-300</v>
       </c>
       <c r="AD100" s="3">
         <v>-300</v>
@@ -9327,10 +9573,10 @@
         <v>-300</v>
       </c>
       <c r="AF100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-900</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>-300</v>
       </c>
       <c r="AH100" s="3">
         <v>-300</v>
@@ -9339,33 +9585,36 @@
         <v>-300</v>
       </c>
       <c r="AJ100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9445,108 +9694,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1100</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>4700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCRAA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCRAA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>MCRAA</t>
   </si>
@@ -656,160 +656,167 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45598</v>
+      </c>
+      <c r="F7" s="2">
         <v>45507</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45409</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45318</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45136</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45045</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44954</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44863</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44772</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44591</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44499</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44317</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44226</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44044</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43953</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43832</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43771</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43680</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43582</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43491</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43400</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43309</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43218</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43127</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43036</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42945</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42854</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42763</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42672</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42581</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -834,89 +841,95 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>33800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>33000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>32800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>31400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>27600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>21400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>21600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>20200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>18900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>12000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>14300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>20300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>22700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>22200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>18600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>20700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>20600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>14900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>16200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>20500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>22400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>22200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>24100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>28100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>29900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>23100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -941,89 +954,95 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>23500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>23400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>23100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>22300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>19600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>16000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>15600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>14700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>13900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>9900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>11600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>15300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>17000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>17000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>14400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>16200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>15300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>11300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>12200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>15500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>16200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>17200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>18300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>20700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>22500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>17800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1048,89 +1067,95 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>10300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>9600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>9700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>9100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>8000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>5400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>6000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>5500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>5000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>5000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>5700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>5200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>4200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>4500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>5300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>4000</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>6200</v>
       </c>
       <c r="AF10" s="3">
         <v>5000</v>
       </c>
       <c r="AG10" s="3">
+        <v>6200</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AI10" s="3">
         <v>5800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>7400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>5300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1168,8 +1193,10 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1275,8 +1302,14 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1382,8 +1415,14 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1408,11 +1447,11 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1489,8 +1528,14 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1515,11 +1560,11 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1596,8 +1641,14 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,8 +1683,10 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1658,89 +1711,95 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>29500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>29600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>29000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>28000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>24700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>20600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>20100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>19400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>18300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>13600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>15000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>19700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>21500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>21400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>18200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>20700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>19500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>15200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>16100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>19900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>20400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>21200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>22300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>25500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>27500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>22500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>24100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1765,89 +1824,95 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>4300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>3400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>3800</v>
       </c>
       <c r="N18" s="3">
         <v>3400</v>
       </c>
       <c r="O18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="P18" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Q18" s="3">
         <v>2900</v>
-      </c>
-      <c r="P18" s="3">
-        <v>800</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>1500</v>
       </c>
       <c r="R18" s="3">
         <v>800</v>
       </c>
       <c r="S18" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T18" s="3">
+        <v>800</v>
+      </c>
+      <c r="U18" s="3">
         <v>600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>400</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>1100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>2000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>1000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>2600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1885,8 +1950,10 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1911,44 +1978,44 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>300</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>200</v>
@@ -1960,10 +2027,10 @@
         <v>200</v>
       </c>
       <c r="AA20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC20" s="3">
         <v>100</v>
@@ -1990,10 +2057,16 @@
         <v>100</v>
       </c>
       <c r="AK20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2099,8 +2172,14 @@
       <c r="AK21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2125,11 +2204,11 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2143,71 +2222,77 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
+      <c r="AD22" s="3">
+        <v>0</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>8</v>
+      <c r="AH22" s="3">
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2232,89 +2317,95 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>4100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>3400</v>
-      </c>
-      <c r="M23" s="3">
-        <v>3500</v>
       </c>
       <c r="N23" s="3">
         <v>3400</v>
       </c>
       <c r="O23" s="3">
+        <v>3500</v>
+      </c>
+      <c r="P23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Q23" s="3">
         <v>3100</v>
-      </c>
-      <c r="P23" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1700</v>
       </c>
       <c r="R23" s="3">
         <v>1000</v>
       </c>
       <c r="S23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U23" s="3">
         <v>700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>1100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>2000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>2600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2339,89 +2430,95 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>400</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>800</v>
-      </c>
       <c r="AF24" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AG24" s="3">
         <v>800</v>
       </c>
       <c r="AH24" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>1000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2527,8 +2624,14 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2553,89 +2656,95 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>2500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>100</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>700</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>1300</v>
       </c>
       <c r="AF26" s="3">
         <v>700</v>
       </c>
       <c r="AG26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI26" s="3">
         <v>1200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>1600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2660,89 +2769,95 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>100</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>700</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>1300</v>
       </c>
       <c r="AF27" s="3">
         <v>700</v>
       </c>
       <c r="AG27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI27" s="3">
         <v>1200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>1600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2848,8 +2963,14 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2874,11 +2995,11 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2904,38 +3025,38 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>400</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
@@ -2955,8 +3076,14 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3062,8 +3189,14 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3169,8 +3302,14 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3195,44 +3334,44 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-300</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-200</v>
@@ -3244,10 +3383,10 @@
         <v>-200</v>
       </c>
       <c r="AA32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AC32" s="3">
         <v>-100</v>
@@ -3274,10 +3413,16 @@
         <v>-100</v>
       </c>
       <c r="AK32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3302,89 +3447,95 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>2500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>400</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>900</v>
       </c>
       <c r="AB33" s="3">
         <v>100</v>
       </c>
       <c r="AC33" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD33" s="3">
         <v>100</v>
       </c>
-      <c r="AD33" s="3">
-        <v>700</v>
-      </c>
       <c r="AE33" s="3">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="AF33" s="3">
         <v>700</v>
       </c>
       <c r="AG33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI33" s="3">
         <v>1200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>1600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3490,8 +3641,14 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3516,201 +3673,213 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>2500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>400</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>900</v>
       </c>
       <c r="AB35" s="3">
         <v>100</v>
       </c>
       <c r="AC35" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD35" s="3">
         <v>100</v>
       </c>
-      <c r="AD35" s="3">
-        <v>700</v>
-      </c>
       <c r="AE35" s="3">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="AF35" s="3">
         <v>700</v>
       </c>
       <c r="AG35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI35" s="3">
         <v>1200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>1600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45598</v>
+      </c>
+      <c r="F38" s="2">
         <v>45507</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45409</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45318</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45136</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45045</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44954</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44863</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44772</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44591</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44499</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44317</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44226</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44044</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43953</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43832</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43771</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43680</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43582</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43491</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43400</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43309</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43218</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43127</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43036</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42945</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42854</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42763</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42672</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42581</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3748,8 +3917,10 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3787,436 +3958,462 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F41" s="3">
         <v>20700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>19600</v>
-      </c>
-      <c r="F41" s="3">
-        <v>18300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>24000</v>
       </c>
       <c r="H41" s="3">
         <v>18300</v>
       </c>
       <c r="I41" s="3">
+        <v>24000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>18300</v>
+      </c>
+      <c r="K41" s="3">
         <v>11100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>15400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>13300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>15300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>22400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>15100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>20700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>23500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>23000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>24700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>19100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>21000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>23200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>17300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>13600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>12800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>20400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>21200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>19200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>27600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>33900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>32300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>29200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>28100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>28100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>23400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>16600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>15700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F42" s="3">
         <v>17300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>28000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>30200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>24100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>21500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>18400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>10700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>10400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>10500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>8700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>6500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>6500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>8600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>10600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>9300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>14200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>13900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>2700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>7200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>10900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>13200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>12100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>9500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>7800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>2200</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="3">
-        <v>500</v>
-      </c>
       <c r="AE42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AF42" s="3">
         <v>500</v>
       </c>
       <c r="AG42" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI42" s="3">
         <v>400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>400</v>
-      </c>
-      <c r="AI42" s="3">
-        <v>500</v>
-      </c>
-      <c r="AJ42" s="3">
-        <v>500</v>
       </c>
       <c r="AK42" s="3">
         <v>500</v>
       </c>
+      <c r="AL42" s="3">
+        <v>500</v>
+      </c>
+      <c r="AM42" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F43" s="3">
         <v>20400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>17400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>16300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>19400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>20300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>21200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>19900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>23600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>26100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>21400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>29800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>23500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>16400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>16500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>14100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>13600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>9000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>13100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>14600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>14200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>13400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>10300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>12400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>14500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>11800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>11000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>12800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>13900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>25000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>12300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>14500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>13600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>27800</v>
+      </c>
+      <c r="F44" s="3">
         <v>23800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>20500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>19800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>18000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>21900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>26600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>29700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>31500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>24500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>18400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>16800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>15600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>14300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>12400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>13700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>15300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>18300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>18100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>19500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>19800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>19800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>16100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>15500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>17900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>18400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>14000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>13300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>17400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>18300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>18900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>19600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>24900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>55900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4241,208 +4438,220 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
-      </c>
-      <c r="V45" s="3">
-        <v>600</v>
-      </c>
-      <c r="W45" s="3">
-        <v>800</v>
       </c>
       <c r="X45" s="3">
         <v>600</v>
       </c>
       <c r="Y45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA45" s="3">
         <v>400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>200</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>400</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>300</v>
       </c>
       <c r="AE45" s="3">
         <v>400</v>
       </c>
       <c r="AF45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH45" s="3">
         <v>2200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>400</v>
-      </c>
-      <c r="AI45" s="3">
-        <v>500</v>
-      </c>
-      <c r="AJ45" s="3">
-        <v>2600</v>
       </c>
       <c r="AK45" s="3">
         <v>500</v>
       </c>
+      <c r="AL45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AM45" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>87300</v>
+      </c>
+      <c r="F46" s="3">
         <v>82500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>85800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>85200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>86200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>82300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>77700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>76100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>79500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>76800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>71200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>68700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>67000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>63100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>62900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>62100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>62700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>63000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>57500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>59200</v>
-      </c>
-      <c r="W46" s="3">
-        <v>59300</v>
-      </c>
-      <c r="X46" s="3">
-        <v>59800</v>
       </c>
       <c r="Y46" s="3">
         <v>59300</v>
       </c>
       <c r="Z46" s="3">
+        <v>59800</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>59300</v>
+      </c>
+      <c r="AB46" s="3">
         <v>59100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>59800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>60200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>59400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>59200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>61500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>60000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>60000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>58300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>58000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>58200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F47" s="3">
         <v>11100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4455,59 +4664,59 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L47" s="3">
-        <v>4000</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>4000</v>
       </c>
       <c r="N47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P47" s="3">
         <v>4100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>4100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>4300</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>3200</v>
-      </c>
-      <c r="R47" s="3">
-        <v>3200</v>
       </c>
       <c r="S47" s="3">
         <v>3200</v>
       </c>
       <c r="T47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="U47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="V47" s="3">
         <v>3800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>7700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>8000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>7900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>7800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>7800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>7600</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>7600</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>7700</v>
       </c>
       <c r="AC47" s="3">
         <v>7600</v>
@@ -4516,114 +4725,120 @@
         <v>7700</v>
       </c>
       <c r="AE47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AG47" s="3">
         <v>7500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AG47" s="3">
-        <v>7200</v>
-      </c>
-      <c r="AH47" s="3">
-        <v>7200</v>
       </c>
       <c r="AI47" s="3">
         <v>7200</v>
       </c>
       <c r="AJ47" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AL47" s="3">
         <v>7100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F48" s="3">
         <v>7300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>6900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>5200</v>
-      </c>
-      <c r="K48" s="3">
-        <v>5300</v>
       </c>
       <c r="L48" s="3">
         <v>5200</v>
       </c>
       <c r="M48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="N48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="O48" s="3">
         <v>5100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>5100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>5500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>5700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>5900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>6100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>6200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>6400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>6600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>6700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>6800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>7100</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>7400</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>7200</v>
       </c>
       <c r="AD48" s="3">
         <v>7400</v>
       </c>
       <c r="AE48" s="3">
-        <v>7600</v>
+        <v>7200</v>
       </c>
       <c r="AF48" s="3">
         <v>7400</v>
@@ -4632,19 +4847,25 @@
         <v>7600</v>
       </c>
       <c r="AH48" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>7800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>8100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4750,8 +4971,14 @@
       <c r="AK49" s="3">
         <v>2800</v>
       </c>
+      <c r="AL49" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AM49" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4857,8 +5084,14 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4964,8 +5197,14 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4973,28 +5212,28 @@
         <v>2800</v>
       </c>
       <c r="E52" s="3">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="F52" s="3">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="G52" s="3">
         <v>3000</v>
       </c>
       <c r="H52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J52" s="3">
         <v>3100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>5300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>2300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>2300</v>
       </c>
       <c r="M52" s="3">
         <v>2300</v>
@@ -5039,16 +5278,16 @@
         <v>2300</v>
       </c>
       <c r="AA52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AC52" s="3">
         <v>3400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>3400</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>2300</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>2300</v>
       </c>
       <c r="AE52" s="3">
         <v>2300</v>
@@ -5071,8 +5310,14 @@
       <c r="AK52" s="3">
         <v>2300</v>
       </c>
+      <c r="AL52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AM52" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5178,115 +5423,127 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>109100</v>
+      </c>
+      <c r="F54" s="3">
         <v>106500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>98900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>97800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>99100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>95500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>92000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>90500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>93900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>91000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>85400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>83000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>81400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>77900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>76700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>76200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>76900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>77900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>76600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>78600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>78700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>79400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>78900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>78700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>80800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>80400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>79300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>79400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>81600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>80000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>80000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>78400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>78300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>78600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5324,8 +5581,10 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5363,8 +5622,10 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5372,106 +5633,112 @@
         <v>3700</v>
       </c>
       <c r="E57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>5200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>2900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>3000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>2400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>2200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>2500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>2500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>3300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>2600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>4700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5479,10 +5746,10 @@
         <v>500</v>
       </c>
       <c r="E58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G58" s="3">
         <v>400</v>
@@ -5491,10 +5758,10 @@
         <v>400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5577,8 +5844,14 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5586,237 +5859,249 @@
         <v>1000</v>
       </c>
       <c r="E59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
-        <v>900</v>
-      </c>
       <c r="G59" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="H59" s="3">
         <v>900</v>
       </c>
       <c r="I59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>900</v>
+      </c>
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>6100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>3900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>4000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>2900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>2400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>3000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F60" s="3">
         <v>7500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>10100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>9800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>4000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>5300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>4200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>4100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>4900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>4800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>4200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>3800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>6400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>5800</v>
-      </c>
-      <c r="AG60" s="3">
-        <v>6200</v>
-      </c>
-      <c r="AH60" s="3">
-        <v>5000</v>
       </c>
       <c r="AI60" s="3">
         <v>6200</v>
       </c>
       <c r="AJ60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AK60" s="3">
+        <v>6200</v>
+      </c>
+      <c r="AL60" s="3">
         <v>7700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F61" s="3">
         <v>1600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -5898,8 +6183,14 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5924,17 +6215,17 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>500</v>
@@ -5943,10 +6234,10 @@
         <v>500</v>
       </c>
       <c r="Q62" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="R62" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="S62" s="3">
         <v>700</v>
@@ -5967,46 +6258,52 @@
         <v>700</v>
       </c>
       <c r="Y62" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA62" s="3">
         <v>600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1200</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3">
         <v>2300</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL62" s="3">
         <v>2300</v>
       </c>
-      <c r="AK62" s="3" t="s">
+      <c r="AM62" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6112,8 +6409,14 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6219,8 +6522,14 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6326,115 +6635,127 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F66" s="3">
         <v>9500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>8000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>10200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>9800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>7200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>6100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>4300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>4700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>6000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>4800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>4700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>6600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>5400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>4200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>3800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>6400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>5800</v>
-      </c>
-      <c r="AG66" s="3">
-        <v>6200</v>
-      </c>
-      <c r="AH66" s="3">
-        <v>5000</v>
       </c>
       <c r="AI66" s="3">
         <v>6200</v>
       </c>
       <c r="AJ66" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AK66" s="3">
+        <v>6200</v>
+      </c>
+      <c r="AL66" s="3">
         <v>7700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6472,8 +6793,10 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6579,8 +6902,14 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6686,8 +7015,14 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6793,8 +7128,14 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6900,115 +7241,127 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>96300</v>
+      </c>
+      <c r="F72" s="3">
         <v>94800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>89200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>87500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>87600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>84700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>83600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>81800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>81500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>79000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>76400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>74200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>71900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>70000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>69900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>69300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>69200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>69500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>71100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>71900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>71700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>71000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>71800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>71700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>72000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>72600</v>
-      </c>
-      <c r="AC72" s="3">
-        <v>72800</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>73200</v>
       </c>
       <c r="AE72" s="3">
         <v>72800</v>
       </c>
       <c r="AF72" s="3">
+        <v>73200</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>72800</v>
+      </c>
+      <c r="AH72" s="3">
         <v>71800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>71400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>71000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>69700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>68500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>68200</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7114,8 +7467,14 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7221,8 +7580,14 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7328,115 +7693,127 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>98600</v>
+      </c>
+      <c r="F76" s="3">
         <v>97100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>91500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>89800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>89800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>86900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>85800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>84100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>83800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>81200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>78700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>76400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>74200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>72200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>72200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>71600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>71500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>71800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>73200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>74300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>74000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>73300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>74100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>74000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>74200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>75000</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>75200</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>75600</v>
       </c>
       <c r="AE76" s="3">
         <v>75200</v>
       </c>
       <c r="AF76" s="3">
+        <v>75600</v>
+      </c>
+      <c r="AG76" s="3">
+        <v>75200</v>
+      </c>
+      <c r="AH76" s="3">
         <v>74200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>73800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>73400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>72100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>70900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7542,120 +7919,132 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45598</v>
+      </c>
+      <c r="F80" s="2">
         <v>45507</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45409</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45318</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45136</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45045</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44954</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44863</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44772</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44591</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44499</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44317</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44226</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44044</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43953</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43832</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43771</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43680</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43582</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43491</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43400</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43309</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43218</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43127</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43036</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42945</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42854</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42763</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42672</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42581</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7680,89 +8069,95 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>2500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>400</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>900</v>
       </c>
       <c r="AB81" s="3">
         <v>100</v>
       </c>
       <c r="AC81" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD81" s="3">
         <v>100</v>
       </c>
-      <c r="AD81" s="3">
-        <v>700</v>
-      </c>
       <c r="AE81" s="3">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="AF81" s="3">
         <v>700</v>
       </c>
       <c r="AG81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI81" s="3">
         <v>1200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>1600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7800,37 +8195,39 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>1500</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>1000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7907,8 +8304,14 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8014,8 +8417,14 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8121,8 +8530,14 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8228,8 +8643,14 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8335,8 +8756,14 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8442,115 +8869,127 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>7200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>10000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>4000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>10400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-5200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>5200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>4100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>3800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>5600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>7100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8588,64 +9027,66 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8672,31 +9113,37 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-200</v>
       </c>
       <c r="AI91" s="3">
         <v>-100</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8802,8 +9249,14 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8909,115 +9362,127 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F94" s="3">
         <v>2300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>1700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-2500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-7900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2800</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>2200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>4900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-7100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>4300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>3600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>2100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>400</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-500</v>
       </c>
       <c r="AF94" s="3">
         <v>-400</v>
       </c>
       <c r="AG94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="AH94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9055,37 +9520,39 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>300</v>
+        <v>1900</v>
       </c>
       <c r="E96" s="3">
         <v>300</v>
       </c>
       <c r="F96" s="3">
-        <v>1700</v>
+        <v>300</v>
       </c>
       <c r="G96" s="3">
         <v>300</v>
       </c>
       <c r="H96" s="3">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="I96" s="3">
         <v>300</v>
       </c>
       <c r="J96" s="3">
+        <v>300</v>
+      </c>
+      <c r="K96" s="3">
+        <v>300</v>
+      </c>
+      <c r="L96" s="3">
         <v>1400</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-300</v>
       </c>
       <c r="M96" s="3">
         <v>-300</v>
@@ -9130,13 +9597,13 @@
         <v>-300</v>
       </c>
       <c r="AA96" s="3">
-        <v>-1500</v>
+        <v>-300</v>
       </c>
       <c r="AB96" s="3">
         <v>-300</v>
       </c>
       <c r="AC96" s="3">
-        <v>-300</v>
+        <v>-1500</v>
       </c>
       <c r="AD96" s="3">
         <v>-300</v>
@@ -9162,8 +9629,14 @@
       <c r="AK96" s="3">
         <v>-300</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9269,8 +9742,14 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9376,8 +9855,14 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9483,37 +9968,43 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-300</v>
+        <v>-1900</v>
       </c>
       <c r="E100" s="3">
         <v>-300</v>
       </c>
       <c r="F100" s="3">
-        <v>-1700</v>
+        <v>-300</v>
       </c>
       <c r="G100" s="3">
         <v>-300</v>
       </c>
       <c r="H100" s="3">
-        <v>-300</v>
+        <v>-1700</v>
       </c>
       <c r="I100" s="3">
         <v>-300</v>
       </c>
       <c r="J100" s="3">
-        <v>-1400</v>
+        <v>-300</v>
       </c>
       <c r="K100" s="3">
         <v>-300</v>
       </c>
       <c r="L100" s="3">
-        <v>-300</v>
+        <v>-1400</v>
       </c>
       <c r="M100" s="3">
         <v>-300</v>
@@ -9525,73 +10016,79 @@
         <v>-300</v>
       </c>
       <c r="P100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-300</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-1600</v>
       </c>
       <c r="Y100" s="3">
         <v>-300</v>
       </c>
       <c r="Z100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>-1500</v>
       </c>
       <c r="AB100" s="3">
         <v>-300</v>
       </c>
       <c r="AC100" s="3">
-        <v>-400</v>
+        <v>-1500</v>
       </c>
       <c r="AD100" s="3">
         <v>-300</v>
       </c>
       <c r="AE100" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AF100" s="3">
         <v>-300</v>
       </c>
       <c r="AG100" s="3">
-        <v>-900</v>
+        <v>-300</v>
       </c>
       <c r="AH100" s="3">
         <v>-300</v>
       </c>
       <c r="AI100" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="AJ100" s="3">
         <v>-300</v>
       </c>
       <c r="AK100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AL100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AM100" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9616,11 +10113,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9697,111 +10194,123 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F102" s="3">
         <v>1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-5700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>5700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>7200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-7100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>7300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-5600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>5500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>5900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>3700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>1900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>1600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>3100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1100</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>4700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>6800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>3400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCRAA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCRAA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="92">
   <si>
     <t>MCRAA</t>
   </si>
@@ -656,167 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E7" s="2">
         <v>45689</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45598</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45507</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45409</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45318</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45227</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45136</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45045</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44954</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44863</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44772</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44591</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44499</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44317</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44226</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44044</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43953</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43832</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43771</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43680</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43582</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43491</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43400</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43309</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43218</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43127</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43036</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42945</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42763</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42672</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42581</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -847,89 +851,92 @@
       <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>33800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>31400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>27600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>21400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>21600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>20700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>20500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>22400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>22200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>24100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>28100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>29900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>23100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -960,89 +967,92 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>23500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>23400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>22300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15300</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>17000</v>
       </c>
       <c r="Z9" s="3">
         <v>17000</v>
       </c>
       <c r="AA9" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AB9" s="3">
         <v>14400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>15500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>16200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>17200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>18300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>20700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>22500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>17800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1073,89 +1083,92 @@
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>10300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5800</v>
-      </c>
-      <c r="AJ10" s="3">
-        <v>7400</v>
       </c>
       <c r="AK10" s="3">
         <v>7400</v>
       </c>
       <c r="AL10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AM10" s="3">
         <v>5300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1195,8 +1208,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1308,8 +1322,11 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1421,8 +1438,11 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1453,8 +1473,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1534,8 +1554,11 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1566,8 +1589,8 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1647,8 +1670,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1685,8 +1711,9 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1717,89 +1744,92 @@
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>29500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>29600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>29000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>18200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>20700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>15200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>16100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>19900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>20400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>22300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>25500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>27500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>22500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>24100</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1830,89 +1860,92 @@
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>4300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>400</v>
       </c>
-      <c r="AB18" s="3">
-        <v>0</v>
-      </c>
       <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
         <v>1100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1952,8 +1985,9 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1984,41 +2018,41 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>200</v>
       </c>
       <c r="S20" s="3">
+        <v>200</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>200</v>
       </c>
       <c r="Y20" s="3">
         <v>200</v>
@@ -2033,7 +2067,7 @@
         <v>200</v>
       </c>
       <c r="AC20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD20" s="3">
         <v>100</v>
@@ -2063,10 +2097,13 @@
         <v>100</v>
       </c>
       <c r="AM20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2178,8 +2215,11 @@
       <c r="AM21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2210,8 +2250,8 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2228,8 +2268,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
@@ -2237,11 +2277,11 @@
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
@@ -2249,11 +2289,11 @@
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
@@ -2261,11 +2301,11 @@
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>8</v>
@@ -2273,11 +2313,11 @@
       <c r="AG22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="3" t="s">
-        <v>8</v>
+      <c r="AH22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
       </c>
       <c r="AJ22" s="3" t="s">
         <v>8</v>
@@ -2285,14 +2325,17 @@
       <c r="AK22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="3" t="s">
+      <c r="AL22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2323,89 +2366,92 @@
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>4100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2436,89 +2482,92 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>100</v>
       </c>
       <c r="AB24" s="3">
         <v>100</v>
       </c>
       <c r="AC24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>400</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>800</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>1000</v>
       </c>
       <c r="AK24" s="3">
         <v>1000</v>
       </c>
       <c r="AL24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AM24" s="3">
         <v>100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2630,8 +2679,11 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2662,89 +2714,92 @@
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="3">
-        <v>2900</v>
+      <c r="M26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N26" s="3">
         <v>2900</v>
       </c>
       <c r="O26" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="P26" s="3">
         <v>2500</v>
       </c>
       <c r="Q26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R26" s="3">
         <v>2200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2775,89 +2830,92 @@
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
-        <v>2900</v>
+      <c r="M27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N27" s="3">
         <v>2900</v>
       </c>
       <c r="O27" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="P27" s="3">
         <v>2500</v>
       </c>
       <c r="Q27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R27" s="3">
         <v>2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2969,8 +3027,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3001,8 +3062,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -3031,8 +3092,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -3040,11 +3101,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3052,14 +3113,14 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>400</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
@@ -3082,8 +3143,11 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3195,8 +3259,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3308,8 +3375,11 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3340,41 +3410,41 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>-200</v>
       </c>
       <c r="S32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-200</v>
       </c>
       <c r="Y32" s="3">
         <v>-200</v>
@@ -3389,7 +3459,7 @@
         <v>-200</v>
       </c>
       <c r="AC32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AD32" s="3">
         <v>-100</v>
@@ -3419,10 +3489,13 @@
         <v>-100</v>
       </c>
       <c r="AM32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AN32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3453,89 +3526,92 @@
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
-        <v>2900</v>
+      <c r="M33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N33" s="3">
         <v>2900</v>
       </c>
       <c r="O33" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="P33" s="3">
         <v>2500</v>
       </c>
       <c r="Q33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R33" s="3">
         <v>2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>900</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>100</v>
       </c>
       <c r="AE33" s="3">
         <v>100</v>
       </c>
       <c r="AF33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG33" s="3">
         <v>700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3647,8 +3723,11 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3679,207 +3758,213 @@
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="3">
-        <v>2900</v>
+      <c r="M35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N35" s="3">
         <v>2900</v>
       </c>
       <c r="O35" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="P35" s="3">
         <v>2500</v>
       </c>
       <c r="Q35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R35" s="3">
         <v>2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>900</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>100</v>
       </c>
       <c r="AE35" s="3">
         <v>100</v>
       </c>
       <c r="AF35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG35" s="3">
         <v>700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E38" s="2">
         <v>45689</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45598</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45507</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45409</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45318</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45227</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45136</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45045</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44954</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44863</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44772</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44591</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44499</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44317</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44226</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44044</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43953</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43832</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43771</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43680</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43582</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43491</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43400</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43309</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43218</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43127</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43036</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42945</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42763</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42672</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42581</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3919,8 +4004,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3960,210 +4046,214 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>22800</v>
-      </c>
-      <c r="E41" s="3">
-        <v>22700</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3">
         <v>20700</v>
       </c>
-      <c r="G41" s="3">
-        <v>19600</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="3">
         <v>18300</v>
       </c>
-      <c r="I41" s="3">
-        <v>24000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>18300</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>20700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>23000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>21000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>23200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>17300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>20400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>21200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>19200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>27600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>33900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>32300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>29200</v>
-      </c>
-      <c r="AH41" s="3">
-        <v>28100</v>
       </c>
       <c r="AI41" s="3">
         <v>28100</v>
       </c>
       <c r="AJ41" s="3">
+        <v>28100</v>
+      </c>
+      <c r="AK41" s="3">
         <v>23400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>16600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>15700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>16600</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>17300</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>21500</v>
+      </c>
+      <c r="L42" s="3">
         <v>18400</v>
       </c>
-      <c r="F42" s="3">
-        <v>17300</v>
-      </c>
-      <c r="G42" s="3">
-        <v>28000</v>
-      </c>
-      <c r="H42" s="3">
-        <v>30200</v>
-      </c>
-      <c r="I42" s="3">
-        <v>24100</v>
-      </c>
-      <c r="J42" s="3">
-        <v>21500</v>
-      </c>
-      <c r="K42" s="3">
-        <v>18400</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>10500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8700</v>
-      </c>
-      <c r="P42" s="3">
-        <v>6500</v>
       </c>
       <c r="Q42" s="3">
         <v>6500</v>
       </c>
       <c r="R42" s="3">
+        <v>6500</v>
+      </c>
+      <c r="S42" s="3">
         <v>8600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>10600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>9300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>14200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>13900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>7200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>10900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>13200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>12100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>9500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>7800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2200</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
-      </c>
       <c r="AF42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AG42" s="3">
         <v>500</v>
@@ -4172,13 +4262,13 @@
         <v>500</v>
       </c>
       <c r="AI42" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AJ42" s="3">
         <v>400</v>
       </c>
       <c r="AK42" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AL42" s="3">
         <v>500</v>
@@ -4186,234 +4276,243 @@
       <c r="AM42" s="3">
         <v>500</v>
       </c>
+      <c r="AN42" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>17000</v>
-      </c>
-      <c r="E43" s="3">
-        <v>17700</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>20400</v>
       </c>
-      <c r="G43" s="3">
-        <v>17400</v>
-      </c>
-      <c r="H43" s="3">
-        <v>16300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>19400</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>20300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>26100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>21400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>29800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>23500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>13400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>10300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>12400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>14500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>11800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>11000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>12800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>13900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>25000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>12300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>14500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>15400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>13600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>28400</v>
-      </c>
-      <c r="E44" s="3">
-        <v>27800</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
         <v>23800</v>
       </c>
-      <c r="G44" s="3">
-        <v>20500</v>
-      </c>
-      <c r="H44" s="3">
-        <v>19800</v>
-      </c>
-      <c r="I44" s="3">
-        <v>18000</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
         <v>21900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>26600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>29700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>31500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>24500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>18400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>16800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>15600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>14300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>15300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>18300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>18100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>19500</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>19800</v>
       </c>
       <c r="Z44" s="3">
         <v>19800</v>
       </c>
       <c r="AA44" s="3">
+        <v>19800</v>
+      </c>
+      <c r="AB44" s="3">
         <v>16100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>15500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>17900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>18400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>14000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>13300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>17400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>18300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>18900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>19600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>24900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>55900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4444,217 +4543,223 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
-      </c>
-      <c r="R45" s="3">
-        <v>300</v>
       </c>
       <c r="S45" s="3">
         <v>300</v>
       </c>
       <c r="T45" s="3">
+        <v>300</v>
+      </c>
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>600</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>400</v>
       </c>
       <c r="AB45" s="3">
         <v>400</v>
       </c>
       <c r="AC45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD45" s="3">
         <v>500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>86200</v>
-      </c>
-      <c r="E46" s="3">
-        <v>87300</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3">
         <v>82500</v>
       </c>
-      <c r="G46" s="3">
-        <v>85800</v>
-      </c>
-      <c r="H46" s="3">
-        <v>85200</v>
-      </c>
-      <c r="I46" s="3">
-        <v>86200</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3">
         <v>82300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>77700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>76100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>79500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>76800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>71200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>68700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>67000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>63100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>62900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>62100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>62700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>63000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>57500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>59200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>59300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>59800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>59300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>59100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>59800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>60200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>59400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>59200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>61500</v>
-      </c>
-      <c r="AH46" s="3">
-        <v>60000</v>
       </c>
       <c r="AI46" s="3">
         <v>60000</v>
       </c>
       <c r="AJ46" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AK46" s="3">
         <v>58300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>58000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>58200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>7300</v>
-      </c>
-      <c r="E47" s="3">
-        <v>9200</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>11100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4670,8 +4775,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>4000</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>4000</v>
@@ -4680,16 +4785,16 @@
         <v>4000</v>
       </c>
       <c r="P47" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="Q47" s="3">
         <v>4100</v>
       </c>
       <c r="R47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="S47" s="3">
         <v>4300</v>
-      </c>
-      <c r="S47" s="3">
-        <v>3200</v>
       </c>
       <c r="T47" s="3">
         <v>3200</v>
@@ -4698,46 +4803,46 @@
         <v>3200</v>
       </c>
       <c r="V47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="W47" s="3">
         <v>3800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7900</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>7800</v>
       </c>
       <c r="AA47" s="3">
         <v>7800</v>
       </c>
       <c r="AB47" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="AC47" s="3">
         <v>7600</v>
       </c>
       <c r="AD47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AE47" s="3">
         <v>7700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AI47" s="3">
-        <v>7200</v>
       </c>
       <c r="AJ47" s="3">
         <v>7200</v>
@@ -4746,149 +4851,155 @@
         <v>7200</v>
       </c>
       <c r="AL47" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="AM47" s="3">
         <v>7100</v>
       </c>
+      <c r="AN47" s="3">
+        <v>7100</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>6900</v>
-      </c>
-      <c r="E48" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3">
         <v>7300</v>
       </c>
-      <c r="G48" s="3">
-        <v>7200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="3">
         <v>7300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5200</v>
-      </c>
-      <c r="O48" s="3">
-        <v>5100</v>
       </c>
       <c r="P48" s="3">
         <v>5100</v>
       </c>
       <c r="Q48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R48" s="3">
         <v>5200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>7900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>2800</v>
-      </c>
-      <c r="E49" s="3">
-        <v>2800</v>
-      </c>
-      <c r="F49" s="3">
-        <v>2800</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G49" s="3">
         <v>2800</v>
       </c>
-      <c r="H49" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I49" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J49" s="3">
-        <v>2800</v>
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K49" s="3">
         <v>2800</v>
@@ -4977,8 +5088,11 @@
       <c r="AM49" s="3">
         <v>2800</v>
       </c>
+      <c r="AN49" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5090,8 +5204,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5203,40 +5320,43 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>2800</v>
       </c>
-      <c r="E52" s="3">
-        <v>2800</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2800</v>
-      </c>
-      <c r="G52" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>3100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>5300</v>
       </c>
       <c r="L52" s="3">
         <v>5300</v>
       </c>
       <c r="M52" s="3">
-        <v>2300</v>
+        <v>5300</v>
       </c>
       <c r="N52" s="3">
         <v>2300</v>
@@ -5284,13 +5404,13 @@
         <v>2300</v>
       </c>
       <c r="AC52" s="3">
-        <v>3400</v>
+        <v>2300</v>
       </c>
       <c r="AD52" s="3">
         <v>3400</v>
       </c>
       <c r="AE52" s="3">
-        <v>2300</v>
+        <v>3400</v>
       </c>
       <c r="AF52" s="3">
         <v>2300</v>
@@ -5316,8 +5436,11 @@
       <c r="AM52" s="3">
         <v>2300</v>
       </c>
+      <c r="AN52" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5429,121 +5552,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>106000</v>
-      </c>
-      <c r="E54" s="3">
-        <v>109100</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3">
         <v>106500</v>
       </c>
-      <c r="G54" s="3">
-        <v>98900</v>
-      </c>
-      <c r="H54" s="3">
-        <v>97800</v>
-      </c>
-      <c r="I54" s="3">
-        <v>99100</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="3">
         <v>95500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>92000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>90500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>93900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>91000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>85400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>83000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>81400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>77900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>76700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>76200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>76900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>77900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>76600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>78600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>78700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>79400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>78900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>78700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>80800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>80400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>79300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>79400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>81600</v>
-      </c>
-      <c r="AH54" s="3">
-        <v>80000</v>
       </c>
       <c r="AI54" s="3">
         <v>80000</v>
       </c>
       <c r="AJ54" s="3">
+        <v>80000</v>
+      </c>
+      <c r="AK54" s="3">
         <v>78400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>78300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>78600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5583,8 +5712,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5624,148 +5754,152 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>3700</v>
       </c>
-      <c r="E57" s="3">
-        <v>4000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="P57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="R57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="T57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="V57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="W57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="X57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AC57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="AD57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AE57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
-        <v>4100</v>
-      </c>
-      <c r="N57" s="3">
-        <v>5200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>2800</v>
-      </c>
-      <c r="P57" s="3">
-        <v>3100</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>3200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>2700</v>
-      </c>
-      <c r="S57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="T57" s="3">
+      <c r="AF57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AG57" s="3">
         <v>2200</v>
-      </c>
-      <c r="U57" s="3">
-        <v>3000</v>
-      </c>
-      <c r="V57" s="3">
-        <v>3900</v>
-      </c>
-      <c r="W57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="X57" s="3">
-        <v>1900</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>3400</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>2600</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>2900</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>2400</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>2200</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>2500</v>
       </c>
       <c r="AH57" s="3">
         <v>2500</v>
       </c>
       <c r="AI57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
-        <v>500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>500</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3">
-        <v>400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5850,261 +5984,270 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1000</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="J59" s="3">
-        <v>900</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1800</v>
-      </c>
-      <c r="V59" s="3">
-        <v>1500</v>
       </c>
       <c r="W59" s="3">
         <v>1500</v>
       </c>
       <c r="X59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y59" s="3">
         <v>1700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2000</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>1800</v>
       </c>
       <c r="AE59" s="3">
         <v>1800</v>
       </c>
       <c r="AF59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AG59" s="3">
         <v>1600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3">
+        <v>7500</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="3">
         <v>6500</v>
       </c>
-      <c r="E60" s="3">
-        <v>8700</v>
-      </c>
-      <c r="F60" s="3">
-        <v>7500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>5700</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
+        <v>6100</v>
+      </c>
+      <c r="M60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="N60" s="3">
+        <v>10100</v>
+      </c>
+      <c r="O60" s="3">
+        <v>9800</v>
+      </c>
+      <c r="P60" s="3">
         <v>6200</v>
       </c>
-      <c r="I60" s="3">
-        <v>7400</v>
-      </c>
-      <c r="J60" s="3">
-        <v>6500</v>
-      </c>
-      <c r="K60" s="3">
-        <v>6100</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="Q60" s="3">
+        <v>6000</v>
+      </c>
+      <c r="R60" s="3">
+        <v>6700</v>
+      </c>
+      <c r="S60" s="3">
+        <v>5100</v>
+      </c>
+      <c r="T60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="U60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V60" s="3">
+        <v>4700</v>
+      </c>
+      <c r="W60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="X60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AD60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AF60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AH60" s="3">
         <v>6400</v>
       </c>
-      <c r="M60" s="3">
-        <v>10100</v>
-      </c>
-      <c r="N60" s="3">
-        <v>9800</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="AI60" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>6200</v>
       </c>
-      <c r="P60" s="3">
-        <v>6000</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>6700</v>
-      </c>
-      <c r="R60" s="3">
-        <v>5100</v>
-      </c>
-      <c r="S60" s="3">
-        <v>3900</v>
-      </c>
-      <c r="T60" s="3">
-        <v>4000</v>
-      </c>
-      <c r="U60" s="3">
-        <v>4700</v>
-      </c>
-      <c r="V60" s="3">
-        <v>5400</v>
-      </c>
-      <c r="W60" s="3">
-        <v>2700</v>
-      </c>
-      <c r="X60" s="3">
-        <v>3600</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>4000</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>5300</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>4200</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>4100</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>4900</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>4800</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>4200</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>3800</v>
-      </c>
-      <c r="AG60" s="3">
-        <v>6400</v>
-      </c>
-      <c r="AH60" s="3">
-        <v>5800</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AL60" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ60" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AK60" s="3">
-        <v>6200</v>
-      </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>1600</v>
       </c>
       <c r="H61" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>1900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -6189,8 +6332,11 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6221,14 +6367,14 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
       <c r="O62" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P62" s="3">
         <v>500</v>
@@ -6240,7 +6386,7 @@
         <v>500</v>
       </c>
       <c r="S62" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="T62" s="3">
         <v>700</v>
@@ -6264,46 +6410,49 @@
         <v>700</v>
       </c>
       <c r="AA62" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AB62" s="3">
         <v>600</v>
       </c>
       <c r="AC62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD62" s="3">
         <v>1700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1200</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI62" s="3">
         <v>2300</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AL62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM62" s="3">
         <v>2300</v>
       </c>
-      <c r="AM62" s="3" t="s">
+      <c r="AN62" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6415,8 +6564,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6528,8 +6680,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6641,121 +6796,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>8300</v>
-      </c>
-      <c r="E66" s="3">
-        <v>10500</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3">
         <v>9500</v>
       </c>
-      <c r="G66" s="3">
-        <v>7400</v>
-      </c>
-      <c r="H66" s="3">
-        <v>8000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="3">
         <v>8600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5600</v>
-      </c>
-      <c r="S66" s="3">
-        <v>4600</v>
       </c>
       <c r="T66" s="3">
         <v>4600</v>
       </c>
       <c r="U66" s="3">
+        <v>4600</v>
+      </c>
+      <c r="V66" s="3">
         <v>5400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>7700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6795,8 +6956,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6908,8 +7070,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7021,8 +7186,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7134,8 +7302,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7247,121 +7418,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>95500</v>
-      </c>
-      <c r="E72" s="3">
-        <v>96300</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
         <v>94800</v>
       </c>
-      <c r="G72" s="3">
-        <v>89200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>87500</v>
-      </c>
-      <c r="I72" s="3">
-        <v>87600</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>84700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>83600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>81800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>81500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>79000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>76400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>74200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>71900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>70000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>69900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>69300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>69200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>69500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>71100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>71900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>71700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>71000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>71800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>71700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>72000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>72600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>72800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>73200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>72800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>71800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>71400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>71000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>69700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>68500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>68200</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7473,8 +7650,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7586,8 +7766,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7699,121 +7882,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>97800</v>
-      </c>
-      <c r="E76" s="3">
-        <v>98600</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3">
         <v>97100</v>
       </c>
-      <c r="G76" s="3">
-        <v>91500</v>
-      </c>
-      <c r="H76" s="3">
-        <v>89800</v>
-      </c>
-      <c r="I76" s="3">
-        <v>89800</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" s="3">
         <v>86900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>85800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>84100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>83800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>81200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>78700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>76400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>74200</v>
-      </c>
-      <c r="R76" s="3">
-        <v>72200</v>
       </c>
       <c r="S76" s="3">
         <v>72200</v>
       </c>
       <c r="T76" s="3">
+        <v>72200</v>
+      </c>
+      <c r="U76" s="3">
         <v>71600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>71500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>71800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>73200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>74300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>74000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>73300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>74100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>74000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>74200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>75000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>75200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>75600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>75200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>74200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>73800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>73400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>72100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>70900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7925,126 +8114,132 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E80" s="2">
         <v>45689</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45598</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45507</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45409</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45318</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45227</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45136</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45045</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44954</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44863</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44772</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44591</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44499</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44317</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44226</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44044</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43953</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43832</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43771</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43680</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43582</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43491</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43400</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43309</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43218</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43127</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43036</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42945</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42763</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42672</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42581</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42490</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8075,89 +8270,92 @@
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M81" s="3">
-        <v>2900</v>
+      <c r="M81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N81" s="3">
         <v>2900</v>
       </c>
       <c r="O81" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="P81" s="3">
         <v>2500</v>
       </c>
       <c r="Q81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R81" s="3">
         <v>2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>900</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>100</v>
       </c>
       <c r="AE81" s="3">
         <v>100</v>
       </c>
       <c r="AF81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG81" s="3">
         <v>700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8197,8 +8395,9 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8208,29 +8407,29 @@
       <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -8310,8 +8509,11 @@
       <c r="AM83" s="3">
         <v>0</v>
       </c>
+      <c r="AN83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8423,8 +8625,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8536,8 +8741,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8649,8 +8857,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8762,8 +8973,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8875,121 +9089,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L89" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M89" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="P89" s="3">
+        <v>10400</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="S89" s="3">
+        <v>400</v>
+      </c>
+      <c r="T89" s="3">
+        <v>300</v>
+      </c>
+      <c r="U89" s="3">
         <v>1200</v>
       </c>
-      <c r="F89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I89" s="3">
-        <v>7200</v>
-      </c>
-      <c r="J89" s="3">
-        <v>10000</v>
-      </c>
-      <c r="K89" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="V89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W89" s="3">
+        <v>5200</v>
+      </c>
+      <c r="X89" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AG89" s="3">
         <v>3800</v>
       </c>
-      <c r="M89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="O89" s="3">
-        <v>10400</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="R89" s="3">
-        <v>400</v>
-      </c>
-      <c r="S89" s="3">
-        <v>300</v>
-      </c>
-      <c r="T89" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>5200</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="AH89" s="3">
         <v>2000</v>
       </c>
-      <c r="X89" s="3">
-        <v>500</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>2200</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>4100</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>1700</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>3800</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9029,49 +9249,50 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
+        <v>100</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-300</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
       </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
@@ -9080,16 +9301,16 @@
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -9119,31 +9340,34 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9255,8 +9479,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9368,121 +9595,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>3800</v>
-      </c>
-      <c r="E94" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>2300</v>
       </c>
-      <c r="G94" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2800</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>2200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>4900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>4300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>3600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>2100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-400</v>
       </c>
-      <c r="AI94" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9522,40 +9755,41 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>1900</v>
-      </c>
-      <c r="E96" s="3">
-        <v>300</v>
-      </c>
-      <c r="F96" s="3">
-        <v>300</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
         <v>300</v>
       </c>
-      <c r="H96" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I96" s="3">
-        <v>300</v>
-      </c>
-      <c r="J96" s="3">
-        <v>300</v>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>300</v>
       </c>
       <c r="L96" s="3">
+        <v>300</v>
+      </c>
+      <c r="M96" s="3">
         <v>1400</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-300</v>
       </c>
       <c r="N96" s="3">
         <v>-300</v>
@@ -9603,10 +9837,10 @@
         <v>-300</v>
       </c>
       <c r="AC96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-300</v>
       </c>
       <c r="AE96" s="3">
         <v>-300</v>
@@ -9635,8 +9869,11 @@
       <c r="AM96" s="3">
         <v>-300</v>
       </c>
+      <c r="AN96" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9748,8 +9985,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9861,8 +10101,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9974,40 +10217,43 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-300</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-300</v>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>-300</v>
       </c>
       <c r="L100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M100" s="3">
         <v>-1400</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-300</v>
       </c>
       <c r="N100" s="3">
         <v>-300</v>
@@ -10022,49 +10268,49 @@
         <v>-300</v>
       </c>
       <c r="R100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S100" s="3">
         <v>-800</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-600</v>
       </c>
       <c r="T100" s="3">
         <v>-600</v>
       </c>
       <c r="U100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V100" s="3">
         <v>-800</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-400</v>
       </c>
       <c r="W100" s="3">
         <v>-400</v>
       </c>
       <c r="X100" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="Y100" s="3">
         <v>-300</v>
       </c>
       <c r="Z100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-1600</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>-300</v>
       </c>
       <c r="AB100" s="3">
         <v>-300</v>
       </c>
       <c r="AC100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-400</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>-300</v>
       </c>
       <c r="AG100" s="3">
         <v>-300</v>
@@ -10073,10 +10319,10 @@
         <v>-300</v>
       </c>
       <c r="AI100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-900</v>
-      </c>
-      <c r="AJ100" s="3">
-        <v>-300</v>
       </c>
       <c r="AK100" s="3">
         <v>-300</v>
@@ -10085,10 +10331,13 @@
         <v>-300</v>
       </c>
       <c r="AM100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10119,8 +10368,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -10200,117 +10449,123 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>7200</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="M102" s="3">
         <v>2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="N102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="O102" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="P102" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="R102" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="S102" s="3">
+        <v>400</v>
+      </c>
+      <c r="T102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="U102" s="3">
+        <v>5500</v>
+      </c>
+      <c r="V102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="W102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="X102" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AE102" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AH102" s="3">
         <v>1100</v>
       </c>
-      <c r="G102" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="I102" s="3">
-        <v>5700</v>
-      </c>
-      <c r="J102" s="3">
-        <v>7200</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="L102" s="3">
-        <v>2000</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="O102" s="3">
-        <v>7300</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="R102" s="3">
-        <v>400</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="T102" s="3">
-        <v>5500</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="W102" s="3">
-        <v>5900</v>
-      </c>
-      <c r="X102" s="3">
-        <v>3700</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>800</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AB102" s="3">
-        <v>1900</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="AD102" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="AE102" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AF102" s="3">
-        <v>3100</v>
-      </c>
-      <c r="AG102" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AH102" s="3">
-        <v>0</v>
-      </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>6800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>3400</v>
       </c>
     </row>
